--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_electrical_equipment.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_electrical_equipment.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="twse_6781" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -587,44 +589,41 @@
           <t>Electrical Equipment</t>
         </is>
       </c>
-      <c r="D2">
-        <v>0.04019999999999999</v>
-      </c>
       <c r="G2">
-        <v>0.1670184696569921</v>
+        <v>0.3159022717531076</v>
       </c>
       <c r="H2">
-        <v>0.1023746701846966</v>
+        <v>0.2441063009001286</v>
       </c>
       <c r="I2">
-        <v>-0.00741424802110818</v>
+        <v>0.2584654950707244</v>
       </c>
       <c r="J2">
-        <v>-0.00741424802110818</v>
+        <v>0.2032431483327222</v>
       </c>
       <c r="K2">
-        <v>-0.416</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="L2">
-        <v>-0.01097625329815303</v>
+        <v>0.2098156879554222</v>
       </c>
       <c r="M2">
-        <v>1.073</v>
+        <v>40.9</v>
       </c>
       <c r="N2">
-        <v>0.03506535947712418</v>
+        <v>0.02287727933773353</v>
       </c>
       <c r="O2">
-        <v>-2.579326923076923</v>
+        <v>0.4177732379979571</v>
       </c>
       <c r="P2">
-        <v>1.073</v>
+        <v>40.9</v>
       </c>
       <c r="Q2">
-        <v>0.03506535947712418</v>
+        <v>0.02287727933773353</v>
       </c>
       <c r="R2">
-        <v>-2.579326923076923</v>
+        <v>0.4177732379979571</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -633,34 +632,532 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>8.68</v>
+        <v>108.1</v>
       </c>
       <c r="V2">
-        <v>0.2836601307189542</v>
+        <v>0.06046537644031771</v>
       </c>
       <c r="W2">
-        <v>-0.01386666666666667</v>
+        <v>0.2809988518943743</v>
       </c>
       <c r="X2">
-        <v>0.06641637753907374</v>
+        <v>0.1201295652012071</v>
       </c>
       <c r="Y2">
-        <v>-0.08028304420574041</v>
+        <v>0.1608692866931672</v>
       </c>
       <c r="Z2">
-        <v>1.556340341655716</v>
+        <v>2.17324477648089</v>
       </c>
       <c r="AA2">
-        <v>-0.01153909329829172</v>
+        <v>0.4416971104696192</v>
       </c>
       <c r="AB2">
-        <v>0.06521614798896629</v>
+        <v>0.1168802334534858</v>
       </c>
       <c r="AC2">
-        <v>-0.07675524128725801</v>
+        <v>0.3248168770161334</v>
       </c>
       <c r="AD2">
-        <v>1</v>
+        <v>106.5</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <v>106.5</v>
+      </c>
+      <c r="AG2">
+        <v>-1.599999999999994</v>
+      </c>
+      <c r="AH2">
+        <v>0.0562212954653434</v>
+      </c>
+      <c r="AI2">
+        <v>0.2171696574225122</v>
+      </c>
+      <c r="AJ2">
+        <v>-0.0008957563542716349</v>
+      </c>
+      <c r="AK2">
+        <v>-0.004185194873136266</v>
+      </c>
+      <c r="AL2">
+        <v>0.901</v>
+      </c>
+      <c r="AM2">
+        <v>-1.619</v>
+      </c>
+      <c r="AN2">
+        <v>0.8418972332015811</v>
+      </c>
+      <c r="AO2">
+        <v>133.8512763596004</v>
+      </c>
+      <c r="AP2">
+        <v>-0.01264822134387347</v>
+      </c>
+      <c r="AQ2">
+        <v>-74.49042618900556</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Advanced Energy Solution Holding Co., Ltd. (TWSE:6781)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Electrical Equipment</t>
+        </is>
+      </c>
+      <c r="G3">
+        <v>0.3159022717531076</v>
+      </c>
+      <c r="H3">
+        <v>0.2441063009001286</v>
+      </c>
+      <c r="I3">
+        <v>0.2584654950707244</v>
+      </c>
+      <c r="J3">
+        <v>0.2032431483327222</v>
+      </c>
+      <c r="K3">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="L3">
+        <v>0.2098156879554222</v>
+      </c>
+      <c r="M3">
+        <v>40.9</v>
+      </c>
+      <c r="N3">
+        <v>0.02287727933773353</v>
+      </c>
+      <c r="O3">
+        <v>0.4177732379979571</v>
+      </c>
+      <c r="P3">
+        <v>40.9</v>
+      </c>
+      <c r="Q3">
+        <v>0.02287727933773353</v>
+      </c>
+      <c r="R3">
+        <v>0.4177732379979571</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>108.1</v>
+      </c>
+      <c r="V3">
+        <v>0.06046537644031771</v>
+      </c>
+      <c r="W3">
+        <v>0.2809988518943743</v>
+      </c>
+      <c r="X3">
+        <v>0.1201295652012071</v>
+      </c>
+      <c r="Y3">
+        <v>0.1608692866931672</v>
+      </c>
+      <c r="Z3">
+        <v>2.17324477648089</v>
+      </c>
+      <c r="AA3">
+        <v>0.4416971104696192</v>
+      </c>
+      <c r="AB3">
+        <v>0.1168802334534858</v>
+      </c>
+      <c r="AC3">
+        <v>0.3248168770161334</v>
+      </c>
+      <c r="AD3">
+        <v>106.5</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>106.5</v>
+      </c>
+      <c r="AG3">
+        <v>-1.599999999999994</v>
+      </c>
+      <c r="AH3">
+        <v>0.0562212954653434</v>
+      </c>
+      <c r="AI3">
+        <v>0.2171696574225122</v>
+      </c>
+      <c r="AJ3">
+        <v>-0.0008957563542716349</v>
+      </c>
+      <c r="AK3">
+        <v>-0.004185194873136266</v>
+      </c>
+      <c r="AL3">
+        <v>0.901</v>
+      </c>
+      <c r="AM3">
+        <v>-1.619</v>
+      </c>
+      <c r="AN3">
+        <v>0.8418972332015811</v>
+      </c>
+      <c r="AO3">
+        <v>133.8512763596004</v>
+      </c>
+      <c r="AP3">
+        <v>-0.01264822134387347</v>
+      </c>
+      <c r="AQ3">
+        <v>-74.49042618900556</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AQ2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_capital</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>actual_equity_value</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>actual_enterprise_value</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_capital</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>actual_debt_rating</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>actual_cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>actual_beta</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Advanced Energy Solution Holding Co., Ltd. (TWSE:6781)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>TWSE:6781</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Electrical Equipment</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Cayman Islands</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0562212954653434</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>1787.8</v>
+      </c>
+      <c r="H2">
+        <v>1925.09011246307</v>
+      </c>
+      <c r="I2">
+        <v>1786.2</v>
+      </c>
+      <c r="J2">
+        <v>1816.99011246307</v>
+      </c>
+      <c r="K2">
+        <v>106.5</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0.116880233453486</v>
+      </c>
+      <c r="N2">
+        <v>0.115557111685962</v>
+      </c>
+      <c r="O2">
+        <v>0.0623341743119266</v>
+      </c>
+      <c r="P2">
+        <v>0.0457</v>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="S2">
+        <v>0.120129565201207</v>
+      </c>
+      <c r="T2">
+        <v>0.115557111685962</v>
+      </c>
+      <c r="U2">
+        <v>1.17040879656858</v>
+      </c>
+      <c r="V2">
+        <v>1.10460689780146</v>
+      </c>
+      <c r="W2">
+        <v>10000000</v>
+      </c>
+      <c r="X2">
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <v>0.0388</v>
+      </c>
+      <c r="AA2">
+        <v>1787.8</v>
+      </c>
+      <c r="AB2">
+        <v>0.06948816980840411</v>
+      </c>
+      <c r="AC2">
+        <v>0.0623341743119266</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
@@ -669,168 +1166,8379 @@
         <v>1</v>
       </c>
       <c r="AG2">
-        <v>-7.68</v>
+        <v>126.5</v>
       </c>
       <c r="AH2">
-        <v>0.03164556962025316</v>
+        <v>5.900000000000006</v>
       </c>
       <c r="AI2">
-        <v>0.03215434083601286</v>
+        <v>27.40000000000001</v>
       </c>
       <c r="AJ2">
-        <v>-0.3350785340314136</v>
+        <v>106.5</v>
       </c>
       <c r="AK2">
-        <v>-0.3425512934879572</v>
+        <v>106.5</v>
       </c>
       <c r="AL2">
-        <v>0.001</v>
+        <v>0.901</v>
       </c>
       <c r="AM2">
-        <v>-0.294</v>
+        <v>106.5</v>
       </c>
       <c r="AN2">
-        <v>0.6711409395973155</v>
-      </c>
-      <c r="AO2">
-        <v>-281</v>
-      </c>
-      <c r="AP2">
-        <v>-5.154362416107382</v>
+        <v>108.1</v>
+      </c>
+      <c r="AO2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="b">
+        <v>1</v>
       </c>
       <c r="AQ2">
-        <v>0.9557823129251702</v>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1155571116859621</v>
+      </c>
+      <c r="C2">
+        <v>1925.090112463065</v>
+      </c>
+      <c r="D2">
+        <v>1816.990112463066</v>
+      </c>
+      <c r="E2">
+        <v>-106.5</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>108.1</v>
+      </c>
+      <c r="H2">
+        <v>1787.8</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>126.5</v>
+      </c>
+      <c r="K2">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L2">
+        <v>120.6</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>120.6</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>120.6</v>
+      </c>
+      <c r="Q2">
+        <v>126.5</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1155571116859621</v>
+      </c>
+      <c r="T2">
+        <v>1.104606897801457</v>
+      </c>
+      <c r="U2">
+        <v>0.0457</v>
+      </c>
+      <c r="V2">
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <v>0.0457</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Cayman Islands</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>StrongLED Lighting Systems (Cayman) Co., Ltd. (TPEX:5281)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Electrical Equipment</t>
-        </is>
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1156261116859621</v>
+      </c>
+      <c r="C3">
+        <v>1904.51521524728</v>
       </c>
       <c r="D3">
-        <v>0.04019999999999999</v>
+        <v>1815.35821524728</v>
+      </c>
+      <c r="E3">
+        <v>-87.557</v>
+      </c>
+      <c r="F3">
+        <v>18.943</v>
       </c>
       <c r="G3">
-        <v>0.1670184696569921</v>
+        <v>108.1</v>
       </c>
       <c r="H3">
-        <v>0.1023746701846966</v>
+        <v>1787.8</v>
       </c>
       <c r="I3">
-        <v>-0.00741424802110818</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>-0.00741424802110818</v>
+        <v>126.5</v>
       </c>
       <c r="K3">
-        <v>-0.416</v>
+        <v>5.900000000000006</v>
       </c>
       <c r="L3">
-        <v>-0.01097625329815303</v>
+        <v>120.6</v>
       </c>
       <c r="M3">
-        <v>1.073</v>
+        <v>0.8656951000000002</v>
       </c>
       <c r="N3">
-        <v>0.03506535947712418</v>
+        <v>119.7343049</v>
       </c>
       <c r="O3">
-        <v>-2.579326923076923</v>
+        <v>0</v>
       </c>
       <c r="P3">
-        <v>1.073</v>
+        <v>119.7343049</v>
       </c>
       <c r="Q3">
-        <v>0.03506535947712418</v>
+        <v>125.6343049</v>
       </c>
       <c r="R3">
-        <v>-2.579326923076923</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S3">
-        <v>0</v>
+        <v>0.1163324360464264</v>
       </c>
       <c r="T3">
-        <v>0</v>
+        <v>1.115764543233795</v>
       </c>
       <c r="U3">
-        <v>8.68</v>
+        <v>0.0457</v>
       </c>
       <c r="V3">
-        <v>0.2836601307189542</v>
+        <v>0</v>
       </c>
       <c r="W3">
-        <v>-0.01386666666666667</v>
-      </c>
-      <c r="X3">
-        <v>0.06641637753907374</v>
+        <v>0.0457</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
       </c>
       <c r="Y3">
-        <v>-0.08028304420574041</v>
+        <v>139.310018042149</v>
       </c>
       <c r="Z3">
-        <v>1.556340341655716</v>
-      </c>
-      <c r="AA3">
-        <v>-0.01153909329829172</v>
-      </c>
-      <c r="AB3">
-        <v>0.06521614798896629</v>
-      </c>
-      <c r="AC3">
-        <v>-0.07675524128725801</v>
-      </c>
-      <c r="AD3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1156951116859621</v>
+      </c>
+      <c r="C4">
+        <v>1883.943246719819</v>
+      </c>
+      <c r="D4">
+        <v>1813.729246719819</v>
+      </c>
+      <c r="E4">
+        <v>-68.614</v>
+      </c>
+      <c r="F4">
+        <v>37.886</v>
+      </c>
+      <c r="G4">
+        <v>108.1</v>
+      </c>
+      <c r="H4">
+        <v>1787.8</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>126.5</v>
+      </c>
+      <c r="K4">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L4">
+        <v>120.6</v>
+      </c>
+      <c r="M4">
+        <v>1.7313902</v>
+      </c>
+      <c r="N4">
+        <v>118.8686098</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>118.8686098</v>
+      </c>
+      <c r="Q4">
+        <v>124.7686098</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1171235833530226</v>
+      </c>
+      <c r="T4">
+        <v>1.127149895715772</v>
+      </c>
+      <c r="U4">
+        <v>0.0457</v>
+      </c>
+      <c r="V4">
+        <v>0</v>
+      </c>
+      <c r="W4">
+        <v>0.0457</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>69.65500902107449</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1157641116859621</v>
+      </c>
+      <c r="C5">
+        <v>1863.374199003783</v>
+      </c>
+      <c r="D5">
+        <v>1812.103199003783</v>
+      </c>
+      <c r="E5">
+        <v>-49.67100000000001</v>
+      </c>
+      <c r="F5">
+        <v>56.82899999999999</v>
+      </c>
+      <c r="G5">
+        <v>108.1</v>
+      </c>
+      <c r="H5">
+        <v>1787.8</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>126.5</v>
+      </c>
+      <c r="K5">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L5">
+        <v>120.6</v>
+      </c>
+      <c r="M5">
+        <v>2.5970853</v>
+      </c>
+      <c r="N5">
+        <v>118.0029147</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>118.0029147</v>
+      </c>
+      <c r="Q5">
+        <v>123.9029147</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1179310429752187</v>
+      </c>
+      <c r="T5">
+        <v>1.138769997733461</v>
+      </c>
+      <c r="U5">
+        <v>0.0457</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0.0457</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>46.43667268071634</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1158331116859621</v>
+      </c>
+      <c r="C6">
+        <v>1842.808064250497</v>
+      </c>
+      <c r="D6">
+        <v>1810.480064250497</v>
+      </c>
+      <c r="E6">
+        <v>-30.72799999999999</v>
+      </c>
+      <c r="F6">
+        <v>75.77200000000001</v>
+      </c>
+      <c r="G6">
+        <v>108.1</v>
+      </c>
+      <c r="H6">
+        <v>1787.8</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>126.5</v>
+      </c>
+      <c r="K6">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L6">
+        <v>120.6</v>
+      </c>
+      <c r="M6">
+        <v>3.462780400000001</v>
+      </c>
+      <c r="N6">
+        <v>117.1372196</v>
+      </c>
+      <c r="O6">
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <v>117.1372196</v>
+      </c>
+      <c r="Q6">
+        <v>123.0372196</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1187553246728772</v>
+      </c>
+      <c r="T6">
+        <v>1.150632185209851</v>
+      </c>
+      <c r="U6">
+        <v>0.0457</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0.0457</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>34.82750451053725</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1159021116859621</v>
+      </c>
+      <c r="C7">
+        <v>1822.24483463938</v>
+      </c>
+      <c r="D7">
+        <v>1808.85983463938</v>
+      </c>
+      <c r="E7">
+        <v>-11.785</v>
+      </c>
+      <c r="F7">
+        <v>94.715</v>
+      </c>
+      <c r="G7">
+        <v>108.1</v>
+      </c>
+      <c r="H7">
+        <v>1787.8</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>126.5</v>
+      </c>
+      <c r="K7">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L7">
+        <v>120.6</v>
+      </c>
+      <c r="M7">
+        <v>4.328475500000001</v>
+      </c>
+      <c r="N7">
+        <v>116.2715245</v>
+      </c>
+      <c r="O7">
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <v>116.2715245</v>
+      </c>
+      <c r="Q7">
+        <v>122.1715245</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1195969596694338</v>
+      </c>
+      <c r="T7">
+        <v>1.162744102948902</v>
+      </c>
+      <c r="U7">
+        <v>0.0457</v>
+      </c>
+      <c r="V7">
+        <v>0</v>
+      </c>
+      <c r="W7">
+        <v>0.0457</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>27.8620036084298</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1159711116859621</v>
+      </c>
+      <c r="C8">
+        <v>1801.68450237782</v>
+      </c>
+      <c r="D8">
+        <v>1807.24250237782</v>
+      </c>
+      <c r="E8">
+        <v>7.157999999999987</v>
+      </c>
+      <c r="F8">
+        <v>113.658</v>
+      </c>
+      <c r="G8">
+        <v>108.1</v>
+      </c>
+      <c r="H8">
+        <v>1787.8</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>126.5</v>
+      </c>
+      <c r="K8">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L8">
+        <v>120.6</v>
+      </c>
+      <c r="M8">
+        <v>5.1941706</v>
+      </c>
+      <c r="N8">
+        <v>115.4058294</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>115.4058294</v>
+      </c>
+      <c r="Q8">
+        <v>121.3058294</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1204565017935767</v>
+      </c>
+      <c r="T8">
+        <v>1.17511372106538</v>
+      </c>
+      <c r="U8">
+        <v>0.0457</v>
+      </c>
+      <c r="V8">
+        <v>0</v>
+      </c>
+      <c r="W8">
+        <v>0.0457</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>23.21833634035817</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1160401116859621</v>
+      </c>
+      <c r="C9">
+        <v>1781.127059701053</v>
+      </c>
+      <c r="D9">
+        <v>1805.628059701054</v>
+      </c>
+      <c r="E9">
+        <v>26.101</v>
+      </c>
+      <c r="F9">
+        <v>132.601</v>
+      </c>
+      <c r="G9">
+        <v>108.1</v>
+      </c>
+      <c r="H9">
+        <v>1787.8</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>126.5</v>
+      </c>
+      <c r="K9">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L9">
+        <v>120.6</v>
+      </c>
+      <c r="M9">
+        <v>6.0598657</v>
+      </c>
+      <c r="N9">
+        <v>114.5401343</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>114.5401343</v>
+      </c>
+      <c r="Q9">
+        <v>120.4401343</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1213345286945829</v>
+      </c>
+      <c r="T9">
+        <v>1.187749352474685</v>
+      </c>
+      <c r="U9">
+        <v>0.0457</v>
+      </c>
+      <c r="V9">
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <v>0.0457</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>19.90143114887843</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1161091116859621</v>
+      </c>
+      <c r="C10">
+        <v>1760.572498872034</v>
+      </c>
+      <c r="D10">
+        <v>1804.016498872034</v>
+      </c>
+      <c r="E10">
+        <v>45.04400000000001</v>
+      </c>
+      <c r="F10">
+        <v>151.544</v>
+      </c>
+      <c r="G10">
+        <v>108.1</v>
+      </c>
+      <c r="H10">
+        <v>1787.8</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>126.5</v>
+      </c>
+      <c r="K10">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L10">
+        <v>120.6</v>
+      </c>
+      <c r="M10">
+        <v>6.925560800000001</v>
+      </c>
+      <c r="N10">
+        <v>113.6744392</v>
+      </c>
+      <c r="O10">
+        <v>0</v>
+      </c>
+      <c r="P10">
+        <v>113.6744392</v>
+      </c>
+      <c r="Q10">
+        <v>119.5744392</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1222316431369153</v>
+      </c>
+      <c r="T10">
+        <v>1.200659671523323</v>
+      </c>
+      <c r="U10">
+        <v>0.0457</v>
+      </c>
+      <c r="V10">
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <v>0.0457</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>17.41375225526862</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1161781116859621</v>
+      </c>
+      <c r="C11">
+        <v>1740.020812181314</v>
+      </c>
+      <c r="D11">
+        <v>1802.407812181315</v>
+      </c>
+      <c r="E11">
+        <v>63.98699999999999</v>
+      </c>
+      <c r="F11">
+        <v>170.487</v>
+      </c>
+      <c r="G11">
+        <v>108.1</v>
+      </c>
+      <c r="H11">
+        <v>1787.8</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>126.5</v>
+      </c>
+      <c r="K11">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L11">
+        <v>120.6</v>
+      </c>
+      <c r="M11">
+        <v>7.7912559</v>
+      </c>
+      <c r="N11">
+        <v>112.8087441</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>112.8087441</v>
+      </c>
+      <c r="Q11">
+        <v>118.7087441</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1231484743801782</v>
+      </c>
+      <c r="T11">
+        <v>1.213853733847755</v>
+      </c>
+      <c r="U11">
+        <v>0.0457</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0.0457</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>15.47889089357211</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1162471116859621</v>
+      </c>
+      <c r="C12">
+        <v>1719.471991946923</v>
+      </c>
+      <c r="D12">
+        <v>1800.801991946923</v>
+      </c>
+      <c r="E12">
+        <v>82.93000000000001</v>
+      </c>
+      <c r="F12">
+        <v>189.43</v>
+      </c>
+      <c r="G12">
+        <v>108.1</v>
+      </c>
+      <c r="H12">
+        <v>1787.8</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>126.5</v>
+      </c>
+      <c r="K12">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L12">
+        <v>120.6</v>
+      </c>
+      <c r="M12">
+        <v>8.656951000000001</v>
+      </c>
+      <c r="N12">
+        <v>111.943049</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>111.943049</v>
+      </c>
+      <c r="Q12">
+        <v>117.843049</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.124085679651069</v>
+      </c>
+      <c r="T12">
+        <v>1.227340997557175</v>
+      </c>
+      <c r="U12">
+        <v>0.0457</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0.0457</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>13.9310018042149</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1164921116859621</v>
+      </c>
+      <c r="C13">
+        <v>1694.850210942612</v>
+      </c>
+      <c r="D13">
+        <v>1795.123210942612</v>
+      </c>
+      <c r="E13">
+        <v>101.873</v>
+      </c>
+      <c r="F13">
+        <v>208.373</v>
+      </c>
+      <c r="G13">
+        <v>108.1</v>
+      </c>
+      <c r="H13">
+        <v>1787.8</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>126.5</v>
+      </c>
+      <c r="K13">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L13">
+        <v>120.6</v>
+      </c>
+      <c r="M13">
+        <v>9.8560429</v>
+      </c>
+      <c r="N13">
+        <v>110.7439571</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>110.7439571</v>
+      </c>
+      <c r="Q13">
+        <v>116.6439571</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1250439457145642</v>
+      </c>
+      <c r="T13">
+        <v>1.241131345844334</v>
+      </c>
+      <c r="U13">
+        <v>0.0473</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0.0473</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>12.23614803868193</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1165771116859621</v>
+      </c>
+      <c r="C14">
+        <v>1673.94538091804</v>
+      </c>
+      <c r="D14">
+        <v>1793.16138091804</v>
+      </c>
+      <c r="E14">
+        <v>120.816</v>
+      </c>
+      <c r="F14">
+        <v>227.316</v>
+      </c>
+      <c r="G14">
+        <v>108.1</v>
+      </c>
+      <c r="H14">
+        <v>1787.8</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>126.5</v>
+      </c>
+      <c r="K14">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L14">
+        <v>120.6</v>
+      </c>
+      <c r="M14">
+        <v>10.7520468</v>
+      </c>
+      <c r="N14">
+        <v>109.8479532</v>
+      </c>
+      <c r="O14">
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <v>109.8479532</v>
+      </c>
+      <c r="Q14">
+        <v>115.7479532</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1260239905522297</v>
+      </c>
+      <c r="T14">
+        <v>1.255235111138019</v>
+      </c>
+      <c r="U14">
+        <v>0.0473</v>
+      </c>
+      <c r="V14">
+        <v>0</v>
+      </c>
+      <c r="W14">
+        <v>0.0473</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>11.21646903545844</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1166621116859621</v>
+      </c>
+      <c r="C15">
+        <v>1653.044834248964</v>
+      </c>
+      <c r="D15">
+        <v>1791.203834248964</v>
+      </c>
+      <c r="E15">
+        <v>139.759</v>
+      </c>
+      <c r="F15">
+        <v>246.259</v>
+      </c>
+      <c r="G15">
+        <v>108.1</v>
+      </c>
+      <c r="H15">
+        <v>1787.8</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>126.5</v>
+      </c>
+      <c r="K15">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L15">
+        <v>120.6</v>
+      </c>
+      <c r="M15">
+        <v>11.6480507</v>
+      </c>
+      <c r="N15">
+        <v>108.9519493</v>
+      </c>
+      <c r="O15">
+        <v>0</v>
+      </c>
+      <c r="P15">
+        <v>108.9519493</v>
+      </c>
+      <c r="Q15">
+        <v>114.8519493</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1270265651562783</v>
+      </c>
+      <c r="T15">
+        <v>1.269663100921215</v>
+      </c>
+      <c r="U15">
+        <v>0.0473</v>
+      </c>
+      <c r="V15">
+        <v>0</v>
+      </c>
+      <c r="W15">
+        <v>0.0473</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>10.35366372503856</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1172791116859621</v>
+      </c>
+      <c r="C16">
+        <v>1620.019453065114</v>
+      </c>
+      <c r="D16">
+        <v>1777.121453065114</v>
+      </c>
+      <c r="E16">
+        <v>158.702</v>
+      </c>
+      <c r="F16">
+        <v>265.202</v>
+      </c>
+      <c r="G16">
+        <v>108.1</v>
+      </c>
+      <c r="H16">
+        <v>1787.8</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>126.5</v>
+      </c>
+      <c r="K16">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L16">
+        <v>120.6</v>
+      </c>
+      <c r="M16">
+        <v>13.5518222</v>
+      </c>
+      <c r="N16">
+        <v>107.0481778</v>
+      </c>
+      <c r="O16">
+        <v>0</v>
+      </c>
+      <c r="P16">
+        <v>107.0481778</v>
+      </c>
+      <c r="Q16">
+        <v>112.9481778</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1280524554487932</v>
+      </c>
+      <c r="T16">
+        <v>1.284426625350531</v>
+      </c>
+      <c r="U16">
+        <v>0.0511</v>
+      </c>
+      <c r="V16">
+        <v>0</v>
+      </c>
+      <c r="W16">
+        <v>0.0511</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>8.899172245633505</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1174021116859621</v>
+      </c>
+      <c r="C17">
+        <v>1598.295536191019</v>
+      </c>
+      <c r="D17">
+        <v>1774.340536191019</v>
+      </c>
+      <c r="E17">
+        <v>177.645</v>
+      </c>
+      <c r="F17">
+        <v>284.145</v>
+      </c>
+      <c r="G17">
+        <v>108.1</v>
+      </c>
+      <c r="H17">
+        <v>1787.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>126.5</v>
+      </c>
+      <c r="K17">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L17">
+        <v>120.6</v>
+      </c>
+      <c r="M17">
+        <v>14.5198095</v>
+      </c>
+      <c r="N17">
+        <v>106.0801905</v>
+      </c>
+      <c r="O17">
+        <v>0</v>
+      </c>
+      <c r="P17">
+        <v>106.0801905</v>
+      </c>
+      <c r="Q17">
+        <v>111.9801905</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.129102484336426</v>
+      </c>
+      <c r="T17">
+        <v>1.299537526825244</v>
+      </c>
+      <c r="U17">
+        <v>0.0511</v>
+      </c>
+      <c r="V17">
+        <v>0</v>
+      </c>
+      <c r="W17">
+        <v>0.0511</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>8.305894095924607</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1175251116859621</v>
+      </c>
+      <c r="C18">
+        <v>1576.580309117883</v>
+      </c>
+      <c r="D18">
+        <v>1771.568309117883</v>
+      </c>
+      <c r="E18">
+        <v>196.588</v>
+      </c>
+      <c r="F18">
+        <v>303.088</v>
+      </c>
+      <c r="G18">
+        <v>108.1</v>
+      </c>
+      <c r="H18">
+        <v>1787.8</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>126.5</v>
+      </c>
+      <c r="K18">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L18">
+        <v>120.6</v>
+      </c>
+      <c r="M18">
+        <v>15.4877968</v>
+      </c>
+      <c r="N18">
+        <v>105.1122032</v>
+      </c>
+      <c r="O18">
+        <v>0</v>
+      </c>
+      <c r="P18">
+        <v>105.1122032</v>
+      </c>
+      <c r="Q18">
+        <v>111.0122032</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1301775139118597</v>
+      </c>
+      <c r="T18">
+        <v>1.315008211668401</v>
+      </c>
+      <c r="U18">
+        <v>0.0511</v>
+      </c>
+      <c r="V18">
+        <v>0</v>
+      </c>
+      <c r="W18">
+        <v>0.0511</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>7.786775714929317</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1179711116859622</v>
+      </c>
+      <c r="C19">
+        <v>1547.65741305427</v>
+      </c>
+      <c r="D19">
+        <v>1761.58841305427</v>
+      </c>
+      <c r="E19">
+        <v>215.531</v>
+      </c>
+      <c r="F19">
+        <v>322.031</v>
+      </c>
+      <c r="G19">
+        <v>108.1</v>
+      </c>
+      <c r="H19">
+        <v>1787.8</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>126.5</v>
+      </c>
+      <c r="K19">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L19">
+        <v>120.6</v>
+      </c>
+      <c r="M19">
+        <v>17.067643</v>
+      </c>
+      <c r="N19">
+        <v>103.532357</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
+        <v>103.532357</v>
+      </c>
+      <c r="Q19">
+        <v>109.432357</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1312784478144122</v>
+      </c>
+      <c r="T19">
+        <v>1.330851684098141</v>
+      </c>
+      <c r="U19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V19">
+        <v>0</v>
+      </c>
+      <c r="W19">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>7.066002025001342</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1181131116859621</v>
+      </c>
+      <c r="C20">
+        <v>1525.560513915321</v>
+      </c>
+      <c r="D20">
+        <v>1758.434513915321</v>
+      </c>
+      <c r="E20">
+        <v>234.474</v>
+      </c>
+      <c r="F20">
+        <v>340.974</v>
+      </c>
+      <c r="G20">
+        <v>108.1</v>
+      </c>
+      <c r="H20">
+        <v>1787.8</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>126.5</v>
+      </c>
+      <c r="K20">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L20">
+        <v>120.6</v>
+      </c>
+      <c r="M20">
+        <v>18.071622</v>
+      </c>
+      <c r="N20">
+        <v>102.528378</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
+        <v>102.528378</v>
+      </c>
+      <c r="Q20">
+        <v>108.428378</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1324062337633685</v>
+      </c>
+      <c r="T20">
+        <v>1.347081582684704</v>
+      </c>
+      <c r="U20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>6.673446356945712</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1182551116859621</v>
+      </c>
+      <c r="C21">
+        <v>1503.474887900738</v>
+      </c>
+      <c r="D21">
+        <v>1755.291887900738</v>
+      </c>
+      <c r="E21">
+        <v>253.417</v>
+      </c>
+      <c r="F21">
+        <v>359.917</v>
+      </c>
+      <c r="G21">
+        <v>108.1</v>
+      </c>
+      <c r="H21">
+        <v>1787.8</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>126.5</v>
+      </c>
+      <c r="K21">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L21">
+        <v>120.6</v>
+      </c>
+      <c r="M21">
+        <v>19.075601</v>
+      </c>
+      <c r="N21">
+        <v>101.524399</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>101.524399</v>
+      </c>
+      <c r="Q21">
+        <v>107.424399</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1335618662789656</v>
+      </c>
+      <c r="T21">
+        <v>1.363712219507971</v>
+      </c>
+      <c r="U21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0.05300000000000001</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>6.322212338159096</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1187971116859621</v>
+      </c>
+      <c r="C22">
+        <v>1472.639355993124</v>
+      </c>
+      <c r="D22">
+        <v>1743.399355993124</v>
+      </c>
+      <c r="E22">
+        <v>272.36</v>
+      </c>
+      <c r="F22">
+        <v>378.86</v>
+      </c>
+      <c r="G22">
+        <v>108.1</v>
+      </c>
+      <c r="H22">
+        <v>1787.8</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>126.5</v>
+      </c>
+      <c r="K22">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L22">
+        <v>120.6</v>
+      </c>
+      <c r="M22">
+        <v>20.8373</v>
+      </c>
+      <c r="N22">
+        <v>99.7627</v>
+      </c>
+      <c r="O22">
+        <v>0</v>
+      </c>
+      <c r="P22">
+        <v>99.7627</v>
+      </c>
+      <c r="Q22">
+        <v>105.6627</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1347463896074527</v>
+      </c>
+      <c r="T22">
+        <v>1.380758622251821</v>
+      </c>
+      <c r="U22">
+        <v>0.055</v>
+      </c>
+      <c r="V22">
+        <v>0</v>
+      </c>
+      <c r="W22">
+        <v>0.055</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>5.787698022296554</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1189591116859621</v>
+      </c>
+      <c r="C23">
+        <v>1450.172979926067</v>
+      </c>
+      <c r="D23">
+        <v>1739.875979926067</v>
+      </c>
+      <c r="E23">
+        <v>291.303</v>
+      </c>
+      <c r="F23">
+        <v>397.803</v>
+      </c>
+      <c r="G23">
+        <v>108.1</v>
+      </c>
+      <c r="H23">
+        <v>1787.8</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>126.5</v>
+      </c>
+      <c r="K23">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L23">
+        <v>120.6</v>
+      </c>
+      <c r="M23">
+        <v>21.879165</v>
+      </c>
+      <c r="N23">
+        <v>98.72083499999999</v>
+      </c>
+      <c r="O23">
+        <v>0</v>
+      </c>
+      <c r="P23">
+        <v>98.72083499999999</v>
+      </c>
+      <c r="Q23">
+        <v>104.620835</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1359609008683065</v>
+      </c>
+      <c r="T23">
+        <v>1.398236579495515</v>
+      </c>
+      <c r="U23">
+        <v>0.055</v>
+      </c>
+      <c r="V23">
+        <v>0</v>
+      </c>
+      <c r="W23">
+        <v>0.055</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>5.512093354568147</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1191211116859621</v>
+      </c>
+      <c r="C24">
+        <v>1427.720816484082</v>
+      </c>
+      <c r="D24">
+        <v>1736.366816484082</v>
+      </c>
+      <c r="E24">
+        <v>310.246</v>
+      </c>
+      <c r="F24">
+        <v>416.746</v>
+      </c>
+      <c r="G24">
+        <v>108.1</v>
+      </c>
+      <c r="H24">
+        <v>1787.8</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>126.5</v>
+      </c>
+      <c r="K24">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L24">
+        <v>120.6</v>
+      </c>
+      <c r="M24">
+        <v>22.92103</v>
+      </c>
+      <c r="N24">
+        <v>97.67896999999999</v>
+      </c>
+      <c r="O24">
+        <v>0</v>
+      </c>
+      <c r="P24">
+        <v>97.67896999999999</v>
+      </c>
+      <c r="Q24">
+        <v>103.57897</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1372065534435412</v>
+      </c>
+      <c r="T24">
+        <v>1.416162689489047</v>
+      </c>
+      <c r="U24">
+        <v>0.055</v>
+      </c>
+      <c r="V24">
+        <v>0</v>
+      </c>
+      <c r="W24">
+        <v>0.055</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>5.261543656633232</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1192831116859621</v>
+      </c>
+      <c r="C25">
+        <v>1405.282779843749</v>
+      </c>
+      <c r="D25">
+        <v>1732.871779843749</v>
+      </c>
+      <c r="E25">
+        <v>329.189</v>
+      </c>
+      <c r="F25">
+        <v>435.689</v>
+      </c>
+      <c r="G25">
+        <v>108.1</v>
+      </c>
+      <c r="H25">
+        <v>1787.8</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>126.5</v>
+      </c>
+      <c r="K25">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L25">
+        <v>120.6</v>
+      </c>
+      <c r="M25">
+        <v>23.962895</v>
+      </c>
+      <c r="N25">
+        <v>96.63710499999999</v>
+      </c>
+      <c r="O25">
+        <v>0</v>
+      </c>
+      <c r="P25">
+        <v>96.63710499999999</v>
+      </c>
+      <c r="Q25">
+        <v>102.537105</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1384845606311196</v>
+      </c>
+      <c r="T25">
+        <v>1.434554412729165</v>
+      </c>
+      <c r="U25">
+        <v>0.055</v>
+      </c>
+      <c r="V25">
+        <v>0</v>
+      </c>
+      <c r="W25">
+        <v>0.055</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>5.032780888953526</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1194451116859621</v>
+      </c>
+      <c r="C26">
+        <v>1382.858784871259</v>
+      </c>
+      <c r="D26">
+        <v>1729.390784871259</v>
+      </c>
+      <c r="E26">
+        <v>348.1319999999999</v>
+      </c>
+      <c r="F26">
+        <v>454.6319999999999</v>
+      </c>
+      <c r="G26">
+        <v>108.1</v>
+      </c>
+      <c r="H26">
+        <v>1787.8</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>126.5</v>
+      </c>
+      <c r="K26">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L26">
+        <v>120.6</v>
+      </c>
+      <c r="M26">
+        <v>25.00476</v>
+      </c>
+      <c r="N26">
+        <v>95.59523999999999</v>
+      </c>
+      <c r="O26">
+        <v>0</v>
+      </c>
+      <c r="P26">
+        <v>95.59523999999999</v>
+      </c>
+      <c r="Q26">
+        <v>101.49524</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1397961995867923</v>
+      </c>
+      <c r="T26">
+        <v>1.453430128686128</v>
+      </c>
+      <c r="U26">
+        <v>0.055</v>
+      </c>
+      <c r="V26">
+        <v>0</v>
+      </c>
+      <c r="W26">
+        <v>0.055</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>4.823081685247129</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.1196071116859621</v>
+      </c>
+      <c r="C27">
+        <v>1360.4487471155</v>
+      </c>
+      <c r="D27">
+        <v>1725.9237471155</v>
+      </c>
+      <c r="E27">
+        <v>367.075</v>
+      </c>
+      <c r="F27">
+        <v>473.575</v>
+      </c>
+      <c r="G27">
+        <v>108.1</v>
+      </c>
+      <c r="H27">
+        <v>1787.8</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>126.5</v>
+      </c>
+      <c r="K27">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L27">
+        <v>120.6</v>
+      </c>
+      <c r="M27">
+        <v>26.046625</v>
+      </c>
+      <c r="N27">
+        <v>94.55337499999999</v>
+      </c>
+      <c r="O27">
+        <v>0</v>
+      </c>
+      <c r="P27">
+        <v>94.55337499999999</v>
+      </c>
+      <c r="Q27">
+        <v>100.453375</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1411428155812828</v>
+      </c>
+      <c r="T27">
+        <v>1.472809197068609</v>
+      </c>
+      <c r="U27">
+        <v>0.055</v>
+      </c>
+      <c r="V27">
+        <v>0</v>
+      </c>
+      <c r="W27">
+        <v>0.055</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>4.630158417837244</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.1207571116859621</v>
+      </c>
+      <c r="C28">
+        <v>1317.288052416984</v>
+      </c>
+      <c r="D28">
+        <v>1701.706052416984</v>
+      </c>
+      <c r="E28">
+        <v>386.018</v>
+      </c>
+      <c r="F28">
+        <v>492.518</v>
+      </c>
+      <c r="G28">
+        <v>108.1</v>
+      </c>
+      <c r="H28">
+        <v>1787.8</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>126.5</v>
+      </c>
+      <c r="K28">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L28">
+        <v>120.6</v>
+      </c>
+      <c r="M28">
+        <v>28.9600584</v>
+      </c>
+      <c r="N28">
+        <v>91.63994159999999</v>
+      </c>
+      <c r="O28">
+        <v>0</v>
+      </c>
+      <c r="P28">
+        <v>91.63994159999999</v>
+      </c>
+      <c r="Q28">
+        <v>97.53994159999999</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1425258266026515</v>
+      </c>
+      <c r="T28">
+        <v>1.492712024056023</v>
+      </c>
+      <c r="U28">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V28">
+        <v>0</v>
+      </c>
+      <c r="W28">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>4.164356243149012</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1209571116859621</v>
+      </c>
+      <c r="C29">
+        <v>1294.202486989606</v>
+      </c>
+      <c r="D29">
+        <v>1697.563486989606</v>
+      </c>
+      <c r="E29">
+        <v>404.961</v>
+      </c>
+      <c r="F29">
+        <v>511.461</v>
+      </c>
+      <c r="G29">
+        <v>108.1</v>
+      </c>
+      <c r="H29">
+        <v>1787.8</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>126.5</v>
+      </c>
+      <c r="K29">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L29">
+        <v>120.6</v>
+      </c>
+      <c r="M29">
+        <v>30.0739068</v>
+      </c>
+      <c r="N29">
+        <v>90.52609319999999</v>
+      </c>
+      <c r="O29">
+        <v>0</v>
+      </c>
+      <c r="P29">
+        <v>90.52609319999999</v>
+      </c>
+      <c r="Q29">
+        <v>96.4260932</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1439467283369344</v>
+      </c>
+      <c r="T29">
+        <v>1.513160133974599</v>
+      </c>
+      <c r="U29">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="V29">
+        <v>0</v>
+      </c>
+      <c r="W29">
+        <v>0.05880000000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>4.010120826736085</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1223331116859621</v>
+      </c>
+      <c r="C30">
+        <v>1247.296355831759</v>
+      </c>
+      <c r="D30">
+        <v>1669.600355831759</v>
+      </c>
+      <c r="E30">
+        <v>423.904</v>
+      </c>
+      <c r="F30">
+        <v>530.404</v>
+      </c>
+      <c r="G30">
+        <v>108.1</v>
+      </c>
+      <c r="H30">
+        <v>1787.8</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>126.5</v>
+      </c>
+      <c r="K30">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L30">
+        <v>120.6</v>
+      </c>
+      <c r="M30">
+        <v>33.415452</v>
+      </c>
+      <c r="N30">
+        <v>87.18454799999999</v>
+      </c>
+      <c r="O30">
+        <v>0</v>
+      </c>
+      <c r="P30">
+        <v>87.18454799999999</v>
+      </c>
+      <c r="Q30">
+        <v>93.084548</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1454070995638363</v>
+      </c>
+      <c r="T30">
+        <v>1.534176246946468</v>
+      </c>
+      <c r="U30">
+        <v>0.063</v>
+      </c>
+      <c r="V30">
+        <v>0</v>
+      </c>
+      <c r="W30">
+        <v>0.063</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>3.609108744062477</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1246341116859621</v>
+      </c>
+      <c r="C31">
+        <v>1183.595504398234</v>
+      </c>
+      <c r="D31">
+        <v>1624.842504398234</v>
+      </c>
+      <c r="E31">
+        <v>442.847</v>
+      </c>
+      <c r="F31">
+        <v>549.347</v>
+      </c>
+      <c r="G31">
+        <v>108.1</v>
+      </c>
+      <c r="H31">
+        <v>1787.8</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>126.5</v>
+      </c>
+      <c r="K31">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L31">
+        <v>120.6</v>
+      </c>
+      <c r="M31">
+        <v>38.5092247</v>
+      </c>
+      <c r="N31">
+        <v>82.09077529999999</v>
+      </c>
+      <c r="O31">
+        <v>0</v>
+      </c>
+      <c r="P31">
+        <v>82.09077529999999</v>
+      </c>
+      <c r="Q31">
+        <v>87.9907753</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1469086080083973</v>
+      </c>
+      <c r="T31">
+        <v>1.555784363100643</v>
+      </c>
+      <c r="U31">
+        <v>0.0701</v>
+      </c>
+      <c r="V31">
+        <v>0</v>
+      </c>
+      <c r="W31">
+        <v>0.0701</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>3.131717164900492</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1249471116859621</v>
+      </c>
+      <c r="C32">
+        <v>1158.748932079634</v>
+      </c>
+      <c r="D32">
+        <v>1618.938932079634</v>
+      </c>
+      <c r="E32">
+        <v>461.79</v>
+      </c>
+      <c r="F32">
+        <v>568.29</v>
+      </c>
+      <c r="G32">
+        <v>108.1</v>
+      </c>
+      <c r="H32">
+        <v>1787.8</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>126.5</v>
+      </c>
+      <c r="K32">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L32">
+        <v>120.6</v>
+      </c>
+      <c r="M32">
+        <v>39.837129</v>
+      </c>
+      <c r="N32">
+        <v>80.76287099999999</v>
+      </c>
+      <c r="O32">
+        <v>0</v>
+      </c>
+      <c r="P32">
+        <v>80.76287099999999</v>
+      </c>
+      <c r="Q32">
+        <v>86.662871</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1484530166942316</v>
+      </c>
+      <c r="T32">
+        <v>1.578009854002081</v>
+      </c>
+      <c r="U32">
+        <v>0.0701</v>
+      </c>
+      <c r="V32">
+        <v>0</v>
+      </c>
+      <c r="W32">
+        <v>0.0701</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>3.027326592737142</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1318631116859621</v>
+      </c>
+      <c r="C33">
+        <v>1019.494226921469</v>
+      </c>
+      <c r="D33">
+        <v>1498.627226921469</v>
+      </c>
+      <c r="E33">
+        <v>480.7329999999999</v>
+      </c>
+      <c r="F33">
+        <v>587.2329999999999</v>
+      </c>
+      <c r="G33">
+        <v>108.1</v>
+      </c>
+      <c r="H33">
+        <v>1787.8</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>126.5</v>
+      </c>
+      <c r="K33">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L33">
+        <v>120.6</v>
+      </c>
+      <c r="M33">
+        <v>53.6730962</v>
+      </c>
+      <c r="N33">
+        <v>66.92690379999999</v>
+      </c>
+      <c r="O33">
+        <v>0</v>
+      </c>
+      <c r="P33">
+        <v>66.92690379999999</v>
+      </c>
+      <c r="Q33">
+        <v>72.8269038</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1500421908492205</v>
+      </c>
+      <c r="T33">
+        <v>1.600879562031097</v>
+      </c>
+      <c r="U33">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V33">
+        <v>0</v>
+      </c>
+      <c r="W33">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>2.246935774873371</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1323891116859621</v>
+      </c>
+      <c r="C34">
+        <v>992.1284744542191</v>
+      </c>
+      <c r="D34">
+        <v>1490.204474454219</v>
+      </c>
+      <c r="E34">
+        <v>499.676</v>
+      </c>
+      <c r="F34">
+        <v>606.176</v>
+      </c>
+      <c r="G34">
+        <v>108.1</v>
+      </c>
+      <c r="H34">
+        <v>1787.8</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>126.5</v>
+      </c>
+      <c r="K34">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L34">
+        <v>120.6</v>
+      </c>
+      <c r="M34">
+        <v>55.40448640000001</v>
+      </c>
+      <c r="N34">
+        <v>65.19551359999998</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>65.19551359999998</v>
+      </c>
+      <c r="Q34">
+        <v>71.09551359999999</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1516781054205325</v>
+      </c>
+      <c r="T34">
+        <v>1.624421908531554</v>
+      </c>
+      <c r="U34">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>2.176719031908578</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1329151116859621</v>
+      </c>
+      <c r="C35">
+        <v>964.8568698388582</v>
+      </c>
+      <c r="D35">
+        <v>1481.875869838858</v>
+      </c>
+      <c r="E35">
+        <v>518.619</v>
+      </c>
+      <c r="F35">
+        <v>625.119</v>
+      </c>
+      <c r="G35">
+        <v>108.1</v>
+      </c>
+      <c r="H35">
+        <v>1787.8</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>126.5</v>
+      </c>
+      <c r="K35">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L35">
+        <v>120.6</v>
+      </c>
+      <c r="M35">
+        <v>57.13587660000001</v>
+      </c>
+      <c r="N35">
+        <v>63.46412339999998</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>63.46412339999998</v>
+      </c>
+      <c r="Q35">
+        <v>69.36412339999998</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1533628532626301</v>
+      </c>
+      <c r="T35">
+        <v>1.648667011643966</v>
+      </c>
+      <c r="U35">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V35">
+        <v>0</v>
+      </c>
+      <c r="W35">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>2.11075784912347</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1334411116859621</v>
+      </c>
+      <c r="C36">
+        <v>937.6778432997611</v>
+      </c>
+      <c r="D36">
+        <v>1473.639843299761</v>
+      </c>
+      <c r="E36">
+        <v>537.562</v>
+      </c>
+      <c r="F36">
+        <v>644.062</v>
+      </c>
+      <c r="G36">
+        <v>108.1</v>
+      </c>
+      <c r="H36">
+        <v>1787.8</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>126.5</v>
+      </c>
+      <c r="K36">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L36">
+        <v>120.6</v>
+      </c>
+      <c r="M36">
+        <v>58.86726680000001</v>
+      </c>
+      <c r="N36">
+        <v>61.73273319999998</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>61.73273319999998</v>
+      </c>
+      <c r="Q36">
+        <v>67.63273319999999</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1550986540696396</v>
+      </c>
+      <c r="T36">
+        <v>1.673646814850692</v>
+      </c>
+      <c r="U36">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0.09140000000000001</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>2.048676735913956</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1413521116859621</v>
+      </c>
+      <c r="C37">
+        <v>805.0563962284442</v>
+      </c>
+      <c r="D37">
+        <v>1359.961396228444</v>
+      </c>
+      <c r="E37">
+        <v>556.505</v>
+      </c>
+      <c r="F37">
+        <v>663.005</v>
+      </c>
+      <c r="G37">
+        <v>108.1</v>
+      </c>
+      <c r="H37">
+        <v>1787.8</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>126.5</v>
+      </c>
+      <c r="K37">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L37">
+        <v>120.6</v>
+      </c>
+      <c r="M37">
+        <v>74.58806250000001</v>
+      </c>
+      <c r="N37">
+        <v>46.01193749999999</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>46.01193749999999</v>
+      </c>
+      <c r="Q37">
+        <v>51.91193749999999</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1568878641322494</v>
+      </c>
+      <c r="T37">
+        <v>1.699395227386857</v>
+      </c>
+      <c r="U37">
+        <v>0.1125</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0.1125</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>1.61688071733999</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1420891116859621</v>
+      </c>
+      <c r="C38">
+        <v>776.4096478598098</v>
+      </c>
+      <c r="D38">
+        <v>1350.25764785981</v>
+      </c>
+      <c r="E38">
+        <v>575.448</v>
+      </c>
+      <c r="F38">
+        <v>681.948</v>
+      </c>
+      <c r="G38">
+        <v>108.1</v>
+      </c>
+      <c r="H38">
+        <v>1787.8</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>126.5</v>
+      </c>
+      <c r="K38">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L38">
+        <v>120.6</v>
+      </c>
+      <c r="M38">
+        <v>76.71915</v>
+      </c>
+      <c r="N38">
+        <v>43.88085</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>43.88085</v>
+      </c>
+      <c r="Q38">
+        <v>49.78085</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1587329870093158</v>
+      </c>
+      <c r="T38">
+        <v>1.725948277814777</v>
+      </c>
+      <c r="U38">
+        <v>0.1125</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0.1125</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>1.571967364080546</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1428261116859621</v>
+      </c>
+      <c r="C39">
+        <v>747.9003969412246</v>
+      </c>
+      <c r="D39">
+        <v>1340.691396941225</v>
+      </c>
+      <c r="E39">
+        <v>594.391</v>
+      </c>
+      <c r="F39">
+        <v>700.891</v>
+      </c>
+      <c r="G39">
+        <v>108.1</v>
+      </c>
+      <c r="H39">
+        <v>1787.8</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>126.5</v>
+      </c>
+      <c r="K39">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L39">
+        <v>120.6</v>
+      </c>
+      <c r="M39">
+        <v>78.85023749999999</v>
+      </c>
+      <c r="N39">
+        <v>41.7497625</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>41.7497625</v>
+      </c>
+      <c r="Q39">
+        <v>47.64976250000001</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1606366852158129</v>
+      </c>
+      <c r="T39">
+        <v>1.753344282224535</v>
+      </c>
+      <c r="U39">
+        <v>0.1125</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0.1125</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>1.529481759645936</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1755211116859621</v>
+      </c>
+      <c r="C40">
+        <v>408.3492283675486</v>
+      </c>
+      <c r="D40">
+        <v>1020.083228367549</v>
+      </c>
+      <c r="E40">
+        <v>613.3339999999999</v>
+      </c>
+      <c r="F40">
+        <v>719.8339999999999</v>
+      </c>
+      <c r="G40">
+        <v>108.1</v>
+      </c>
+      <c r="H40">
+        <v>1787.8</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>126.5</v>
+      </c>
+      <c r="K40">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L40">
+        <v>120.6</v>
+      </c>
+      <c r="M40">
+        <v>141.5193644</v>
+      </c>
+      <c r="N40">
+        <v>-20.91936440000001</v>
+      </c>
+      <c r="O40">
+        <v>-0</v>
+      </c>
+      <c r="P40">
+        <v>-20.91936440000001</v>
+      </c>
+      <c r="Q40">
+        <v>-15.0193644</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1626017930418744</v>
+      </c>
+      <c r="T40">
+        <v>1.781624028712027</v>
+      </c>
+      <c r="U40">
+        <v>0.1966</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0.1966</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.8521801981750562</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1770991116859622</v>
+      </c>
+      <c r="C41">
+        <v>377.7670260997918</v>
+      </c>
+      <c r="D41">
+        <v>1008.444026099792</v>
+      </c>
+      <c r="E41">
+        <v>632.277</v>
+      </c>
+      <c r="F41">
+        <v>738.777</v>
+      </c>
+      <c r="G41">
+        <v>108.1</v>
+      </c>
+      <c r="H41">
+        <v>1787.8</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>126.5</v>
+      </c>
+      <c r="K41">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L41">
+        <v>120.6</v>
+      </c>
+      <c r="M41">
+        <v>145.2435582</v>
+      </c>
+      <c r="N41">
+        <v>-24.6435582</v>
+      </c>
+      <c r="O41">
+        <v>-0</v>
+      </c>
+      <c r="P41">
+        <v>-24.6435582</v>
+      </c>
+      <c r="Q41">
+        <v>-18.7435582</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1646313306327248</v>
+      </c>
+      <c r="T41">
+        <v>1.810830980002389</v>
+      </c>
+      <c r="U41">
+        <v>0.1966</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0.1966</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.8303294238628753</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1786771116859621</v>
+      </c>
+      <c r="C42">
+        <v>347.4474352193756</v>
+      </c>
+      <c r="D42">
+        <v>997.0674352193757</v>
+      </c>
+      <c r="E42">
+        <v>651.22</v>
+      </c>
+      <c r="F42">
+        <v>757.72</v>
+      </c>
+      <c r="G42">
+        <v>108.1</v>
+      </c>
+      <c r="H42">
+        <v>1787.8</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>126.5</v>
+      </c>
+      <c r="K42">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L42">
+        <v>120.6</v>
+      </c>
+      <c r="M42">
+        <v>148.967752</v>
+      </c>
+      <c r="N42">
+        <v>-28.367752</v>
+      </c>
+      <c r="O42">
+        <v>-0</v>
+      </c>
+      <c r="P42">
+        <v>-28.367752</v>
+      </c>
+      <c r="Q42">
+        <v>-22.46775199999999</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1667285194766036</v>
+      </c>
+      <c r="T42">
+        <v>1.841011496335762</v>
+      </c>
+      <c r="U42">
+        <v>0.1966</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0.1966</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.8095711882663035</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1873071116859621</v>
+      </c>
+      <c r="C43">
+        <v>270.5631563926825</v>
+      </c>
+      <c r="D43">
+        <v>939.1261563926826</v>
+      </c>
+      <c r="E43">
+        <v>670.163</v>
+      </c>
+      <c r="F43">
+        <v>776.663</v>
+      </c>
+      <c r="G43">
+        <v>108.1</v>
+      </c>
+      <c r="H43">
+        <v>1787.8</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>126.5</v>
+      </c>
+      <c r="K43">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L43">
+        <v>120.6</v>
+      </c>
+      <c r="M43">
+        <v>166.0505494</v>
+      </c>
+      <c r="N43">
+        <v>-45.4505494</v>
+      </c>
+      <c r="O43">
+        <v>-0</v>
+      </c>
+      <c r="P43">
+        <v>-45.4505494</v>
+      </c>
+      <c r="Q43">
+        <v>-39.55054939999999</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1688967994677324</v>
+      </c>
+      <c r="T43">
+        <v>1.872215081019418</v>
+      </c>
+      <c r="U43">
+        <v>0.2138</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0.2138</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.7262848598560554</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1890571116859621</v>
+      </c>
+      <c r="C44">
+        <v>240.6824326786657</v>
+      </c>
+      <c r="D44">
+        <v>928.1884326786658</v>
+      </c>
+      <c r="E44">
+        <v>689.106</v>
+      </c>
+      <c r="F44">
+        <v>795.606</v>
+      </c>
+      <c r="G44">
+        <v>108.1</v>
+      </c>
+      <c r="H44">
+        <v>1787.8</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>126.5</v>
+      </c>
+      <c r="K44">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L44">
+        <v>120.6</v>
+      </c>
+      <c r="M44">
+        <v>170.1005628</v>
+      </c>
+      <c r="N44">
+        <v>-49.50056279999998</v>
+      </c>
+      <c r="O44">
+        <v>-0</v>
+      </c>
+      <c r="P44">
+        <v>-49.50056279999998</v>
+      </c>
+      <c r="Q44">
+        <v>-43.60056279999998</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1711398477344175</v>
+      </c>
+      <c r="T44">
+        <v>1.904494651381822</v>
+      </c>
+      <c r="U44">
+        <v>0.2138</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0.2138</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.708992363192816</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1908071116859621</v>
+      </c>
+      <c r="C45">
+        <v>211.0535526617925</v>
+      </c>
+      <c r="D45">
+        <v>917.5025526617926</v>
+      </c>
+      <c r="E45">
+        <v>708.049</v>
+      </c>
+      <c r="F45">
+        <v>814.549</v>
+      </c>
+      <c r="G45">
+        <v>108.1</v>
+      </c>
+      <c r="H45">
+        <v>1787.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>126.5</v>
+      </c>
+      <c r="K45">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L45">
+        <v>120.6</v>
+      </c>
+      <c r="M45">
+        <v>174.1505762</v>
+      </c>
+      <c r="N45">
+        <v>-53.55057619999999</v>
+      </c>
+      <c r="O45">
+        <v>-0</v>
+      </c>
+      <c r="P45">
+        <v>-53.55057619999999</v>
+      </c>
+      <c r="Q45">
+        <v>-47.65057619999999</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1734615994490563</v>
+      </c>
+      <c r="T45">
+        <v>1.93790683824817</v>
+      </c>
+      <c r="U45">
+        <v>0.2138</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0.2138</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.6925041686999598</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1925571116859621</v>
+      </c>
+      <c r="C46">
+        <v>181.6679171989366</v>
+      </c>
+      <c r="D46">
+        <v>907.0599171989365</v>
+      </c>
+      <c r="E46">
+        <v>726.992</v>
+      </c>
+      <c r="F46">
+        <v>833.492</v>
+      </c>
+      <c r="G46">
+        <v>108.1</v>
+      </c>
+      <c r="H46">
+        <v>1787.8</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>126.5</v>
+      </c>
+      <c r="K46">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L46">
+        <v>120.6</v>
+      </c>
+      <c r="M46">
+        <v>178.2005896</v>
+      </c>
+      <c r="N46">
+        <v>-57.60058959999998</v>
+      </c>
+      <c r="O46">
+        <v>-0</v>
+      </c>
+      <c r="P46">
+        <v>-57.60058959999998</v>
+      </c>
+      <c r="Q46">
+        <v>-51.70058959999997</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1758662708677895</v>
+      </c>
+      <c r="T46">
+        <v>1.972512317502602</v>
+      </c>
+      <c r="U46">
+        <v>0.2138</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0.2138</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.6767654375931426</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1943071116859621</v>
+      </c>
+      <c r="C47">
+        <v>152.5173142289595</v>
+      </c>
+      <c r="D47">
+        <v>896.8523142289595</v>
+      </c>
+      <c r="E47">
+        <v>745.9349999999999</v>
+      </c>
+      <c r="F47">
+        <v>852.4349999999999</v>
+      </c>
+      <c r="G47">
+        <v>108.1</v>
+      </c>
+      <c r="H47">
+        <v>1787.8</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>126.5</v>
+      </c>
+      <c r="K47">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L47">
+        <v>120.6</v>
+      </c>
+      <c r="M47">
+        <v>182.250603</v>
+      </c>
+      <c r="N47">
+        <v>-61.65060299999999</v>
+      </c>
+      <c r="O47">
+        <v>-0</v>
+      </c>
+      <c r="P47">
+        <v>-61.65060299999999</v>
+      </c>
+      <c r="Q47">
+        <v>-55.75060299999998</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1783583848835675</v>
+      </c>
+      <c r="T47">
+        <v>2.008376177820831</v>
+      </c>
+      <c r="U47">
+        <v>0.2138</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0.2138</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.6617262056466282</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1960571116859621</v>
+      </c>
+      <c r="C48">
+        <v>123.593897234942</v>
+      </c>
+      <c r="D48">
+        <v>886.871897234942</v>
+      </c>
+      <c r="E48">
+        <v>764.878</v>
+      </c>
+      <c r="F48">
+        <v>871.378</v>
+      </c>
+      <c r="G48">
+        <v>108.1</v>
+      </c>
+      <c r="H48">
+        <v>1787.8</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>126.5</v>
+      </c>
+      <c r="K48">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L48">
+        <v>120.6</v>
+      </c>
+      <c r="M48">
+        <v>186.3006164</v>
+      </c>
+      <c r="N48">
+        <v>-65.7006164</v>
+      </c>
+      <c r="O48">
+        <v>-0</v>
+      </c>
+      <c r="P48">
+        <v>-65.7006164</v>
+      </c>
+      <c r="Q48">
+        <v>-59.8006164</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.1809427994184484</v>
+      </c>
+      <c r="T48">
+        <v>2.045568329261957</v>
+      </c>
+      <c r="U48">
+        <v>0.2138</v>
+      </c>
+      <c r="V48">
+        <v>0</v>
+      </c>
+      <c r="W48">
+        <v>0.2138</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.6473408533499624</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1978071116859622</v>
+      </c>
+      <c r="C49">
+        <v>94.89016512865498</v>
+      </c>
+      <c r="D49">
+        <v>877.111165128655</v>
+      </c>
+      <c r="E49">
+        <v>783.821</v>
+      </c>
+      <c r="F49">
+        <v>890.321</v>
+      </c>
+      <c r="G49">
+        <v>108.1</v>
+      </c>
+      <c r="H49">
+        <v>1787.8</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>126.5</v>
+      </c>
+      <c r="K49">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L49">
+        <v>120.6</v>
+      </c>
+      <c r="M49">
+        <v>190.3506298</v>
+      </c>
+      <c r="N49">
+        <v>-69.75062980000001</v>
+      </c>
+      <c r="O49">
+        <v>-0</v>
+      </c>
+      <c r="P49">
+        <v>-69.75062980000001</v>
+      </c>
+      <c r="Q49">
+        <v>-63.85062980000001</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1836247390301172</v>
+      </c>
+      <c r="T49">
+        <v>2.084163958115957</v>
+      </c>
+      <c r="U49">
+        <v>0.2138</v>
+      </c>
+      <c r="V49">
+        <v>0</v>
+      </c>
+      <c r="W49">
+        <v>0.2138</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.6335676437042185</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1995571116859621</v>
+      </c>
+      <c r="C50">
+        <v>66.3989434488974</v>
+      </c>
+      <c r="D50">
+        <v>867.5629434488973</v>
+      </c>
+      <c r="E50">
+        <v>802.7639999999999</v>
+      </c>
+      <c r="F50">
+        <v>909.2639999999999</v>
+      </c>
+      <c r="G50">
+        <v>108.1</v>
+      </c>
+      <c r="H50">
+        <v>1787.8</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>126.5</v>
+      </c>
+      <c r="K50">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L50">
+        <v>120.6</v>
+      </c>
+      <c r="M50">
+        <v>194.4006432</v>
+      </c>
+      <c r="N50">
+        <v>-73.80064319999997</v>
+      </c>
+      <c r="O50">
+        <v>-0</v>
+      </c>
+      <c r="P50">
+        <v>-73.80064319999997</v>
+      </c>
+      <c r="Q50">
+        <v>-67.90064319999996</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1864098301653118</v>
+      </c>
+      <c r="T50">
+        <v>2.124244034233571</v>
+      </c>
+      <c r="U50">
+        <v>0.2138</v>
+      </c>
+      <c r="V50">
+        <v>0</v>
+      </c>
+      <c r="W50">
+        <v>0.2138</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.620368317793714</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.2013071116859621</v>
+      </c>
+      <c r="C51">
+        <v>38.11336677465624</v>
+      </c>
+      <c r="D51">
+        <v>858.2203667746562</v>
+      </c>
+      <c r="E51">
+        <v>821.707</v>
+      </c>
+      <c r="F51">
+        <v>928.207</v>
+      </c>
+      <c r="G51">
+        <v>108.1</v>
+      </c>
+      <c r="H51">
+        <v>1787.8</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>126.5</v>
+      </c>
+      <c r="K51">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L51">
+        <v>120.6</v>
+      </c>
+      <c r="M51">
+        <v>198.4506566</v>
+      </c>
+      <c r="N51">
+        <v>-77.85065660000001</v>
+      </c>
+      <c r="O51">
+        <v>-0</v>
+      </c>
+      <c r="P51">
+        <v>-77.85065660000001</v>
+      </c>
+      <c r="Q51">
+        <v>-71.9506566</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.18930414056071</v>
+      </c>
+      <c r="T51">
+        <v>2.165895878042072</v>
+      </c>
+      <c r="U51">
+        <v>0.2138</v>
+      </c>
+      <c r="V51">
+        <v>0</v>
+      </c>
+      <c r="W51">
+        <v>0.2138</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.6077077398795565</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.2030571116859621</v>
+      </c>
+      <c r="C52">
+        <v>10.02686226249193</v>
+      </c>
+      <c r="D52">
+        <v>849.0768622624919</v>
+      </c>
+      <c r="E52">
+        <v>840.65</v>
+      </c>
+      <c r="F52">
+        <v>947.15</v>
+      </c>
+      <c r="G52">
+        <v>108.1</v>
+      </c>
+      <c r="H52">
+        <v>1787.8</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>126.5</v>
+      </c>
+      <c r="K52">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L52">
+        <v>120.6</v>
+      </c>
+      <c r="M52">
+        <v>202.50067</v>
+      </c>
+      <c r="N52">
+        <v>-81.90066999999999</v>
+      </c>
+      <c r="O52">
+        <v>-0</v>
+      </c>
+      <c r="P52">
+        <v>-81.90066999999999</v>
+      </c>
+      <c r="Q52">
+        <v>-76.00066999999999</v>
+      </c>
+      <c r="R52">
         <v>1</v>
       </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>1</v>
-      </c>
-      <c r="AG3">
-        <v>-7.68</v>
-      </c>
-      <c r="AH3">
-        <v>0.03164556962025316</v>
-      </c>
-      <c r="AI3">
-        <v>0.03215434083601286</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.3350785340314136</v>
-      </c>
-      <c r="AK3">
-        <v>-0.3425512934879572</v>
-      </c>
-      <c r="AL3">
-        <v>0.001</v>
-      </c>
-      <c r="AM3">
-        <v>-0.294</v>
-      </c>
-      <c r="AN3">
-        <v>0.6711409395973155</v>
-      </c>
-      <c r="AO3">
-        <v>-281</v>
-      </c>
-      <c r="AP3">
-        <v>-5.154362416107382</v>
-      </c>
-      <c r="AQ3">
-        <v>0.9557823129251702</v>
+      <c r="S52">
+        <v>0.1923142233719242</v>
+      </c>
+      <c r="T52">
+        <v>2.209213795602914</v>
+      </c>
+      <c r="U52">
+        <v>0.2138</v>
+      </c>
+      <c r="V52">
+        <v>0</v>
+      </c>
+      <c r="W52">
+        <v>0.2138</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.5955535850819654</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.2048071116859621</v>
+      </c>
+      <c r="C53">
+        <v>-17.86686577481169</v>
+      </c>
+      <c r="D53">
+        <v>840.1261342251883</v>
+      </c>
+      <c r="E53">
+        <v>859.593</v>
+      </c>
+      <c r="F53">
+        <v>966.093</v>
+      </c>
+      <c r="G53">
+        <v>108.1</v>
+      </c>
+      <c r="H53">
+        <v>1787.8</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>126.5</v>
+      </c>
+      <c r="K53">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L53">
+        <v>120.6</v>
+      </c>
+      <c r="M53">
+        <v>206.5506834</v>
+      </c>
+      <c r="N53">
+        <v>-85.95068339999997</v>
+      </c>
+      <c r="O53">
+        <v>-0</v>
+      </c>
+      <c r="P53">
+        <v>-85.95068339999997</v>
+      </c>
+      <c r="Q53">
+        <v>-80.05068339999997</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1954471667060451</v>
+      </c>
+      <c r="T53">
+        <v>2.254299791431545</v>
+      </c>
+      <c r="U53">
+        <v>0.2138</v>
+      </c>
+      <c r="V53">
+        <v>0</v>
+      </c>
+      <c r="W53">
+        <v>0.2138</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.5838760638058484</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.2065571116859621</v>
+      </c>
+      <c r="C54">
+        <v>-45.57385032436889</v>
+      </c>
+      <c r="D54">
+        <v>831.3621496756311</v>
+      </c>
+      <c r="E54">
+        <v>878.5360000000001</v>
+      </c>
+      <c r="F54">
+        <v>985.0360000000001</v>
+      </c>
+      <c r="G54">
+        <v>108.1</v>
+      </c>
+      <c r="H54">
+        <v>1787.8</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>126.5</v>
+      </c>
+      <c r="K54">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L54">
+        <v>120.6</v>
+      </c>
+      <c r="M54">
+        <v>210.6006968</v>
+      </c>
+      <c r="N54">
+        <v>-90.00069680000001</v>
+      </c>
+      <c r="O54">
+        <v>-0</v>
+      </c>
+      <c r="P54">
+        <v>-90.00069680000001</v>
+      </c>
+      <c r="Q54">
+        <v>-84.10069680000001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1987106493457544</v>
+      </c>
+      <c r="T54">
+        <v>2.301264370419702</v>
+      </c>
+      <c r="U54">
+        <v>0.2138</v>
+      </c>
+      <c r="V54">
+        <v>0</v>
+      </c>
+      <c r="W54">
+        <v>0.2138</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.5726476779634282</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2083071116859621</v>
+      </c>
+      <c r="C55">
+        <v>-73.09987523383541</v>
+      </c>
+      <c r="D55">
+        <v>822.7791247661646</v>
+      </c>
+      <c r="E55">
+        <v>897.479</v>
+      </c>
+      <c r="F55">
+        <v>1003.979</v>
+      </c>
+      <c r="G55">
+        <v>108.1</v>
+      </c>
+      <c r="H55">
+        <v>1787.8</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>126.5</v>
+      </c>
+      <c r="K55">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L55">
+        <v>120.6</v>
+      </c>
+      <c r="M55">
+        <v>214.6507102</v>
+      </c>
+      <c r="N55">
+        <v>-94.0507102</v>
+      </c>
+      <c r="O55">
+        <v>-0</v>
+      </c>
+      <c r="P55">
+        <v>-94.0507102</v>
+      </c>
+      <c r="Q55">
+        <v>-88.15071019999999</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.2021130035871535</v>
+      </c>
+      <c r="T55">
+        <v>2.350227442130759</v>
+      </c>
+      <c r="U55">
+        <v>0.2138</v>
+      </c>
+      <c r="V55">
+        <v>0</v>
+      </c>
+      <c r="W55">
+        <v>0.2138</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.561843004794307</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2100571116859621</v>
+      </c>
+      <c r="C56">
+        <v>-100.4504879406356</v>
+      </c>
+      <c r="D56">
+        <v>814.3715120593644</v>
+      </c>
+      <c r="E56">
+        <v>916.422</v>
+      </c>
+      <c r="F56">
+        <v>1022.922</v>
+      </c>
+      <c r="G56">
+        <v>108.1</v>
+      </c>
+      <c r="H56">
+        <v>1787.8</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>126.5</v>
+      </c>
+      <c r="K56">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L56">
+        <v>120.6</v>
+      </c>
+      <c r="M56">
+        <v>218.7007236</v>
+      </c>
+      <c r="N56">
+        <v>-98.10072360000001</v>
+      </c>
+      <c r="O56">
+        <v>-0</v>
+      </c>
+      <c r="P56">
+        <v>-98.10072360000001</v>
+      </c>
+      <c r="Q56">
+        <v>-92.2007236</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.2056632862738307</v>
+      </c>
+      <c r="T56">
+        <v>2.401319343046645</v>
+      </c>
+      <c r="U56">
+        <v>0.2138</v>
+      </c>
+      <c r="V56">
+        <v>0</v>
+      </c>
+      <c r="W56">
+        <v>0.2138</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.5514385047055235</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2118071116859621</v>
+      </c>
+      <c r="C57">
+        <v>-127.6310114286339</v>
+      </c>
+      <c r="D57">
+        <v>806.1339885713661</v>
+      </c>
+      <c r="E57">
+        <v>935.365</v>
+      </c>
+      <c r="F57">
+        <v>1041.865</v>
+      </c>
+      <c r="G57">
+        <v>108.1</v>
+      </c>
+      <c r="H57">
+        <v>1787.8</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>126.5</v>
+      </c>
+      <c r="K57">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L57">
+        <v>120.6</v>
+      </c>
+      <c r="M57">
+        <v>222.750737</v>
+      </c>
+      <c r="N57">
+        <v>-102.150737</v>
+      </c>
+      <c r="O57">
+        <v>-0</v>
+      </c>
+      <c r="P57">
+        <v>-102.150737</v>
+      </c>
+      <c r="Q57">
+        <v>-96.25073699999999</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.2093713593021381</v>
+      </c>
+      <c r="T57">
+        <v>2.454681995114349</v>
+      </c>
+      <c r="U57">
+        <v>0.2138</v>
+      </c>
+      <c r="V57">
+        <v>0</v>
+      </c>
+      <c r="W57">
+        <v>0.2138</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.541412350074514</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2135571116859621</v>
+      </c>
+      <c r="C58">
+        <v>-154.6465554664125</v>
+      </c>
+      <c r="D58">
+        <v>798.0614445335875</v>
+      </c>
+      <c r="E58">
+        <v>954.308</v>
+      </c>
+      <c r="F58">
+        <v>1060.808</v>
+      </c>
+      <c r="G58">
+        <v>108.1</v>
+      </c>
+      <c r="H58">
+        <v>1787.8</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>126.5</v>
+      </c>
+      <c r="K58">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L58">
+        <v>120.6</v>
+      </c>
+      <c r="M58">
+        <v>226.8007504</v>
+      </c>
+      <c r="N58">
+        <v>-106.2007504</v>
+      </c>
+      <c r="O58">
+        <v>-0</v>
+      </c>
+      <c r="P58">
+        <v>-106.2007504</v>
+      </c>
+      <c r="Q58">
+        <v>-100.3007504</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.2132479811044594</v>
+      </c>
+      <c r="T58">
+        <v>2.510470222276039</v>
+      </c>
+      <c r="U58">
+        <v>0.2138</v>
+      </c>
+      <c r="V58">
+        <v>0</v>
+      </c>
+      <c r="W58">
+        <v>0.2138</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.531744272394612</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2153071116859621</v>
+      </c>
+      <c r="C59">
+        <v>-181.5020271770063</v>
+      </c>
+      <c r="D59">
+        <v>790.1489728229939</v>
+      </c>
+      <c r="E59">
+        <v>973.2510000000002</v>
+      </c>
+      <c r="F59">
+        <v>1079.751</v>
+      </c>
+      <c r="G59">
+        <v>108.1</v>
+      </c>
+      <c r="H59">
+        <v>1787.8</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>126.5</v>
+      </c>
+      <c r="K59">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L59">
+        <v>120.6</v>
+      </c>
+      <c r="M59">
+        <v>230.8507638</v>
+      </c>
+      <c r="N59">
+        <v>-110.2507638</v>
+      </c>
+      <c r="O59">
+        <v>-0</v>
+      </c>
+      <c r="P59">
+        <v>-110.2507638</v>
+      </c>
+      <c r="Q59">
+        <v>-104.3507638</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.2173049108975864</v>
+      </c>
+      <c r="T59">
+        <v>2.568853250701063</v>
+      </c>
+      <c r="U59">
+        <v>0.2138</v>
+      </c>
+      <c r="V59">
+        <v>0</v>
+      </c>
+      <c r="W59">
+        <v>0.2138</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.5224154255104958</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2170571116859621</v>
+      </c>
+      <c r="C60">
+        <v>-208.2021409850446</v>
+      </c>
+      <c r="D60">
+        <v>782.3918590149553</v>
+      </c>
+      <c r="E60">
+        <v>992.194</v>
+      </c>
+      <c r="F60">
+        <v>1098.694</v>
+      </c>
+      <c r="G60">
+        <v>108.1</v>
+      </c>
+      <c r="H60">
+        <v>1787.8</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>126.5</v>
+      </c>
+      <c r="K60">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L60">
+        <v>120.6</v>
+      </c>
+      <c r="M60">
+        <v>234.9007772</v>
+      </c>
+      <c r="N60">
+        <v>-114.3007772</v>
+      </c>
+      <c r="O60">
+        <v>-0</v>
+      </c>
+      <c r="P60">
+        <v>-114.3007772</v>
+      </c>
+      <c r="Q60">
+        <v>-108.4007772</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.2215550278237193</v>
+      </c>
+      <c r="T60">
+        <v>2.630016423336802</v>
+      </c>
+      <c r="U60">
+        <v>0.2138</v>
+      </c>
+      <c r="V60">
+        <v>0</v>
+      </c>
+      <c r="W60">
+        <v>0.2138</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.5134082630016943</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2188071116859621</v>
+      </c>
+      <c r="C61">
+        <v>-234.7514279836649</v>
+      </c>
+      <c r="D61">
+        <v>774.785572016335</v>
+      </c>
+      <c r="E61">
+        <v>1011.137</v>
+      </c>
+      <c r="F61">
+        <v>1117.637</v>
+      </c>
+      <c r="G61">
+        <v>108.1</v>
+      </c>
+      <c r="H61">
+        <v>1787.8</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>126.5</v>
+      </c>
+      <c r="K61">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L61">
+        <v>120.6</v>
+      </c>
+      <c r="M61">
+        <v>238.9507906</v>
+      </c>
+      <c r="N61">
+        <v>-118.3507906</v>
+      </c>
+      <c r="O61">
+        <v>-0</v>
+      </c>
+      <c r="P61">
+        <v>-118.3507906</v>
+      </c>
+      <c r="Q61">
+        <v>-112.4507906</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.2260124675267368</v>
+      </c>
+      <c r="T61">
+        <v>2.694163165369407</v>
+      </c>
+      <c r="U61">
+        <v>0.2138</v>
+      </c>
+      <c r="V61">
+        <v>0</v>
+      </c>
+      <c r="W61">
+        <v>0.2138</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.504706428035564</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2355571116859621</v>
+      </c>
+      <c r="C62">
+        <v>-319.6521878840382</v>
+      </c>
+      <c r="D62">
+        <v>708.8278121159617</v>
+      </c>
+      <c r="E62">
+        <v>1030.08</v>
+      </c>
+      <c r="F62">
+        <v>1136.58</v>
+      </c>
+      <c r="G62">
+        <v>108.1</v>
+      </c>
+      <c r="H62">
+        <v>1787.8</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>126.5</v>
+      </c>
+      <c r="K62">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L62">
+        <v>120.6</v>
+      </c>
+      <c r="M62">
+        <v>271.415304</v>
+      </c>
+      <c r="N62">
+        <v>-150.815304</v>
+      </c>
+      <c r="O62">
+        <v>-0</v>
+      </c>
+      <c r="P62">
+        <v>-150.815304</v>
+      </c>
+      <c r="Q62">
+        <v>-144.915304</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.2306927792149053</v>
+      </c>
+      <c r="T62">
+        <v>2.761517244503642</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0</v>
+      </c>
+      <c r="W62">
+        <v>0.2388</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.444337508691109</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2375571116859621</v>
+      </c>
+      <c r="C63">
+        <v>-345.7277911514466</v>
+      </c>
+      <c r="D63">
+        <v>701.6952088485533</v>
+      </c>
+      <c r="E63">
+        <v>1049.023</v>
+      </c>
+      <c r="F63">
+        <v>1155.523</v>
+      </c>
+      <c r="G63">
+        <v>108.1</v>
+      </c>
+      <c r="H63">
+        <v>1787.8</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>126.5</v>
+      </c>
+      <c r="K63">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L63">
+        <v>120.6</v>
+      </c>
+      <c r="M63">
+        <v>275.9388924</v>
+      </c>
+      <c r="N63">
+        <v>-155.3388924</v>
+      </c>
+      <c r="O63">
+        <v>-0</v>
+      </c>
+      <c r="P63">
+        <v>-155.3388924</v>
+      </c>
+      <c r="Q63">
+        <v>-149.4388924</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.2356131068870824</v>
+      </c>
+      <c r="T63">
+        <v>2.832325378978095</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0</v>
+      </c>
+      <c r="W63">
+        <v>0.2388</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.4370532872371564</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2395571116859621</v>
+      </c>
+      <c r="C64">
+        <v>-371.6612803346759</v>
+      </c>
+      <c r="D64">
+        <v>694.704719665324</v>
+      </c>
+      <c r="E64">
+        <v>1067.966</v>
+      </c>
+      <c r="F64">
+        <v>1174.466</v>
+      </c>
+      <c r="G64">
+        <v>108.1</v>
+      </c>
+      <c r="H64">
+        <v>1787.8</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>126.5</v>
+      </c>
+      <c r="K64">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L64">
+        <v>120.6</v>
+      </c>
+      <c r="M64">
+        <v>280.4624808</v>
+      </c>
+      <c r="N64">
+        <v>-159.8624808</v>
+      </c>
+      <c r="O64">
+        <v>-0</v>
+      </c>
+      <c r="P64">
+        <v>-159.8624808</v>
+      </c>
+      <c r="Q64">
+        <v>-153.9624808</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.2407923991735846</v>
+      </c>
+      <c r="T64">
+        <v>2.906860257372256</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0</v>
+      </c>
+      <c r="W64">
+        <v>0.2388</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.4300040406688153</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2415571116859621</v>
+      </c>
+      <c r="C65">
+        <v>-397.456860881802</v>
+      </c>
+      <c r="D65">
+        <v>687.8521391181979</v>
+      </c>
+      <c r="E65">
+        <v>1086.909</v>
+      </c>
+      <c r="F65">
+        <v>1193.409</v>
+      </c>
+      <c r="G65">
+        <v>108.1</v>
+      </c>
+      <c r="H65">
+        <v>1787.8</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>126.5</v>
+      </c>
+      <c r="K65">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L65">
+        <v>120.6</v>
+      </c>
+      <c r="M65">
+        <v>284.9860692</v>
+      </c>
+      <c r="N65">
+        <v>-164.3860692</v>
+      </c>
+      <c r="O65">
+        <v>-0</v>
+      </c>
+      <c r="P65">
+        <v>-164.3860692</v>
+      </c>
+      <c r="Q65">
+        <v>-158.4860692</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.246251653205303</v>
+      </c>
+      <c r="T65">
+        <v>2.985424048112046</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0</v>
+      </c>
+      <c r="W65">
+        <v>0.2388</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.4231785797058182</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2435571116859621</v>
+      </c>
+      <c r="C66">
+        <v>-423.118573931175</v>
+      </c>
+      <c r="D66">
+        <v>681.1334260688251</v>
+      </c>
+      <c r="E66">
+        <v>1105.852</v>
+      </c>
+      <c r="F66">
+        <v>1212.352</v>
+      </c>
+      <c r="G66">
+        <v>108.1</v>
+      </c>
+      <c r="H66">
+        <v>1787.8</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>126.5</v>
+      </c>
+      <c r="K66">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L66">
+        <v>120.6</v>
+      </c>
+      <c r="M66">
+        <v>289.5096576</v>
+      </c>
+      <c r="N66">
+        <v>-168.9096576</v>
+      </c>
+      <c r="O66">
+        <v>-0</v>
+      </c>
+      <c r="P66">
+        <v>-168.9096576</v>
+      </c>
+      <c r="Q66">
+        <v>-163.0096576</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.2520141991276725</v>
+      </c>
+      <c r="T66">
+        <v>3.068352493892936</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0</v>
+      </c>
+      <c r="W66">
+        <v>0.2388</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.4165664143979146</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2455571116859622</v>
+      </c>
+      <c r="C67">
+        <v>-448.6503042584141</v>
+      </c>
+      <c r="D67">
+        <v>674.544695741586</v>
+      </c>
+      <c r="E67">
+        <v>1124.795</v>
+      </c>
+      <c r="F67">
+        <v>1231.295</v>
+      </c>
+      <c r="G67">
+        <v>108.1</v>
+      </c>
+      <c r="H67">
+        <v>1787.8</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>126.5</v>
+      </c>
+      <c r="K67">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L67">
+        <v>120.6</v>
+      </c>
+      <c r="M67">
+        <v>294.033246</v>
+      </c>
+      <c r="N67">
+        <v>-173.433246</v>
+      </c>
+      <c r="O67">
+        <v>-0</v>
+      </c>
+      <c r="P67">
+        <v>-173.433246</v>
+      </c>
+      <c r="Q67">
+        <v>-167.533246</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2581060333884633</v>
+      </c>
+      <c r="T67">
+        <v>3.156019708004163</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0</v>
+      </c>
+      <c r="W67">
+        <v>0.2388</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.4101577003302544</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2475571116859621</v>
+      </c>
+      <c r="C68">
+        <v>-474.0557877665816</v>
+      </c>
+      <c r="D68">
+        <v>668.0822122334184</v>
+      </c>
+      <c r="E68">
+        <v>1143.738</v>
+      </c>
+      <c r="F68">
+        <v>1250.238</v>
+      </c>
+      <c r="G68">
+        <v>108.1</v>
+      </c>
+      <c r="H68">
+        <v>1787.8</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>126.5</v>
+      </c>
+      <c r="K68">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L68">
+        <v>120.6</v>
+      </c>
+      <c r="M68">
+        <v>298.5568344</v>
+      </c>
+      <c r="N68">
+        <v>-177.9568344</v>
+      </c>
+      <c r="O68">
+        <v>-0</v>
+      </c>
+      <c r="P68">
+        <v>-177.9568344</v>
+      </c>
+      <c r="Q68">
+        <v>-172.0568344</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2645562108410651</v>
+      </c>
+      <c r="T68">
+        <v>3.248843817063109</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0</v>
+      </c>
+      <c r="W68">
+        <v>0.2388</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.40394318971919</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2495571116859621</v>
+      </c>
+      <c r="C69">
+        <v>-499.3386185498853</v>
+      </c>
+      <c r="D69">
+        <v>661.7423814501147</v>
+      </c>
+      <c r="E69">
+        <v>1162.681</v>
+      </c>
+      <c r="F69">
+        <v>1269.181</v>
+      </c>
+      <c r="G69">
+        <v>108.1</v>
+      </c>
+      <c r="H69">
+        <v>1787.8</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>126.5</v>
+      </c>
+      <c r="K69">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L69">
+        <v>120.6</v>
+      </c>
+      <c r="M69">
+        <v>303.0804228</v>
+      </c>
+      <c r="N69">
+        <v>-182.4804228</v>
+      </c>
+      <c r="O69">
+        <v>-0</v>
+      </c>
+      <c r="P69">
+        <v>-182.4804228</v>
+      </c>
+      <c r="Q69">
+        <v>-176.5804228</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2713973081392792</v>
+      </c>
+      <c r="T69">
+        <v>3.347293629701385</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0</v>
+      </c>
+      <c r="W69">
+        <v>0.2388</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.3979141868875603</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2515571116859622</v>
+      </c>
+      <c r="C70">
+        <v>-524.5022555589724</v>
+      </c>
+      <c r="D70">
+        <v>655.5217444410276</v>
+      </c>
+      <c r="E70">
+        <v>1181.624</v>
+      </c>
+      <c r="F70">
+        <v>1288.124</v>
+      </c>
+      <c r="G70">
+        <v>108.1</v>
+      </c>
+      <c r="H70">
+        <v>1787.8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>126.5</v>
+      </c>
+      <c r="K70">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L70">
+        <v>120.6</v>
+      </c>
+      <c r="M70">
+        <v>307.6040112</v>
+      </c>
+      <c r="N70">
+        <v>-187.0040112</v>
+      </c>
+      <c r="O70">
+        <v>-0</v>
+      </c>
+      <c r="P70">
+        <v>-187.0040112</v>
+      </c>
+      <c r="Q70">
+        <v>-181.1040112</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2786659740186317</v>
+      </c>
+      <c r="T70">
+        <v>3.451896555629554</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0</v>
+      </c>
+      <c r="W70">
+        <v>0.2388</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.3920625076686256</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2535571116859622</v>
+      </c>
+      <c r="C71">
+        <v>-549.5500288937861</v>
+      </c>
+      <c r="D71">
+        <v>649.4169711062139</v>
+      </c>
+      <c r="E71">
+        <v>1200.567</v>
+      </c>
+      <c r="F71">
+        <v>1307.067</v>
+      </c>
+      <c r="G71">
+        <v>108.1</v>
+      </c>
+      <c r="H71">
+        <v>1787.8</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>126.5</v>
+      </c>
+      <c r="K71">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L71">
+        <v>120.6</v>
+      </c>
+      <c r="M71">
+        <v>312.1275996</v>
+      </c>
+      <c r="N71">
+        <v>-191.5275996</v>
+      </c>
+      <c r="O71">
+        <v>-0</v>
+      </c>
+      <c r="P71">
+        <v>-191.5275996</v>
+      </c>
+      <c r="Q71">
+        <v>-185.6275996</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2864035860837488</v>
+      </c>
+      <c r="T71">
+        <v>3.563248057424055</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0</v>
+      </c>
+      <c r="W71">
+        <v>0.2388</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.3863804423400948</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2555571116859621</v>
+      </c>
+      <c r="C72">
+        <v>-574.485145748038</v>
+      </c>
+      <c r="D72">
+        <v>643.424854251962</v>
+      </c>
+      <c r="E72">
+        <v>1219.51</v>
+      </c>
+      <c r="F72">
+        <v>1326.01</v>
+      </c>
+      <c r="G72">
+        <v>108.1</v>
+      </c>
+      <c r="H72">
+        <v>1787.8</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>126.5</v>
+      </c>
+      <c r="K72">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L72">
+        <v>120.6</v>
+      </c>
+      <c r="M72">
+        <v>316.651188</v>
+      </c>
+      <c r="N72">
+        <v>-196.051188</v>
+      </c>
+      <c r="O72">
+        <v>-0</v>
+      </c>
+      <c r="P72">
+        <v>-196.051188</v>
+      </c>
+      <c r="Q72">
+        <v>-190.151188</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2946570389532071</v>
+      </c>
+      <c r="T72">
+        <v>3.682022992671524</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0</v>
+      </c>
+      <c r="W72">
+        <v>0.2388</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.3808607217352363</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2575571116859621</v>
+      </c>
+      <c r="C73">
+        <v>-599.3106960275976</v>
+      </c>
+      <c r="D73">
+        <v>637.5423039724024</v>
+      </c>
+      <c r="E73">
+        <v>1238.453</v>
+      </c>
+      <c r="F73">
+        <v>1344.953</v>
+      </c>
+      <c r="G73">
+        <v>108.1</v>
+      </c>
+      <c r="H73">
+        <v>1787.8</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>126.5</v>
+      </c>
+      <c r="K73">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L73">
+        <v>120.6</v>
+      </c>
+      <c r="M73">
+        <v>321.1747764</v>
+      </c>
+      <c r="N73">
+        <v>-200.5747764</v>
+      </c>
+      <c r="O73">
+        <v>-0</v>
+      </c>
+      <c r="P73">
+        <v>-200.5747764</v>
+      </c>
+      <c r="Q73">
+        <v>-194.6747764</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.3034796954688349</v>
+      </c>
+      <c r="T73">
+        <v>3.808989302763644</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0</v>
+      </c>
+      <c r="W73">
+        <v>0.2388</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.3754964862178386</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2595571116859621</v>
+      </c>
+      <c r="C74">
+        <v>-624.0296576634731</v>
+      </c>
+      <c r="D74">
+        <v>631.7663423365268</v>
+      </c>
+      <c r="E74">
+        <v>1257.396</v>
+      </c>
+      <c r="F74">
+        <v>1363.896</v>
+      </c>
+      <c r="G74">
+        <v>108.1</v>
+      </c>
+      <c r="H74">
+        <v>1787.8</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>126.5</v>
+      </c>
+      <c r="K74">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L74">
+        <v>120.6</v>
+      </c>
+      <c r="M74">
+        <v>325.6983648</v>
+      </c>
+      <c r="N74">
+        <v>-205.0983648</v>
+      </c>
+      <c r="O74">
+        <v>-0</v>
+      </c>
+      <c r="P74">
+        <v>-205.0983648</v>
+      </c>
+      <c r="Q74">
+        <v>-199.1983648</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.312932541735579</v>
+      </c>
+      <c r="T74">
+        <v>3.945024635005203</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0</v>
+      </c>
+      <c r="W74">
+        <v>0.2388</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.3702812572425909</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2615571116859621</v>
+      </c>
+      <c r="C75">
+        <v>-648.6449016385806</v>
+      </c>
+      <c r="D75">
+        <v>626.0940983614194</v>
+      </c>
+      <c r="E75">
+        <v>1276.339</v>
+      </c>
+      <c r="F75">
+        <v>1382.839</v>
+      </c>
+      <c r="G75">
+        <v>108.1</v>
+      </c>
+      <c r="H75">
+        <v>1787.8</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>126.5</v>
+      </c>
+      <c r="K75">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L75">
+        <v>120.6</v>
+      </c>
+      <c r="M75">
+        <v>330.2219532</v>
+      </c>
+      <c r="N75">
+        <v>-209.6219532</v>
+      </c>
+      <c r="O75">
+        <v>-0</v>
+      </c>
+      <c r="P75">
+        <v>-209.6219532</v>
+      </c>
+      <c r="Q75">
+        <v>-203.7219532</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.3230855988368967</v>
+      </c>
+      <c r="T75">
+        <v>4.091136658523914</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0</v>
+      </c>
+      <c r="W75">
+        <v>0.2388</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.3652089112529663</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2635571116859621</v>
+      </c>
+      <c r="C76">
+        <v>-673.1591967461295</v>
+      </c>
+      <c r="D76">
+        <v>620.5228032538704</v>
+      </c>
+      <c r="E76">
+        <v>1295.282</v>
+      </c>
+      <c r="F76">
+        <v>1401.782</v>
+      </c>
+      <c r="G76">
+        <v>108.1</v>
+      </c>
+      <c r="H76">
+        <v>1787.8</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>126.5</v>
+      </c>
+      <c r="K76">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L76">
+        <v>120.6</v>
+      </c>
+      <c r="M76">
+        <v>334.7455416</v>
+      </c>
+      <c r="N76">
+        <v>-214.1455416</v>
+      </c>
+      <c r="O76">
+        <v>-0</v>
+      </c>
+      <c r="P76">
+        <v>-214.1455416</v>
+      </c>
+      <c r="Q76">
+        <v>-208.2455416</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.3340196603306235</v>
+      </c>
+      <c r="T76">
+        <v>4.248488068467141</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0</v>
+      </c>
+      <c r="W76">
+        <v>0.2388</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.3602736556954937</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2655571116859621</v>
+      </c>
+      <c r="C77">
+        <v>-697.5752140961938</v>
+      </c>
+      <c r="D77">
+        <v>615.0497859038061</v>
+      </c>
+      <c r="E77">
+        <v>1314.225</v>
+      </c>
+      <c r="F77">
+        <v>1420.725</v>
+      </c>
+      <c r="G77">
+        <v>108.1</v>
+      </c>
+      <c r="H77">
+        <v>1787.8</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>126.5</v>
+      </c>
+      <c r="K77">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L77">
+        <v>120.6</v>
+      </c>
+      <c r="M77">
+        <v>339.26913</v>
+      </c>
+      <c r="N77">
+        <v>-218.66913</v>
+      </c>
+      <c r="O77">
+        <v>-0</v>
+      </c>
+      <c r="P77">
+        <v>-218.66913</v>
+      </c>
+      <c r="Q77">
+        <v>-212.76913</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.3458284467438485</v>
+      </c>
+      <c r="T77">
+        <v>4.418427591205828</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0</v>
+      </c>
+      <c r="W77">
+        <v>0.2388</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.3554700069528872</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2675571116859621</v>
+      </c>
+      <c r="C78">
+        <v>-721.8955313858801</v>
+      </c>
+      <c r="D78">
+        <v>609.6724686141198</v>
+      </c>
+      <c r="E78">
+        <v>1333.168</v>
+      </c>
+      <c r="F78">
+        <v>1439.668</v>
+      </c>
+      <c r="G78">
+        <v>108.1</v>
+      </c>
+      <c r="H78">
+        <v>1787.8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>126.5</v>
+      </c>
+      <c r="K78">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L78">
+        <v>120.6</v>
+      </c>
+      <c r="M78">
+        <v>343.7927184</v>
+      </c>
+      <c r="N78">
+        <v>-223.1927184</v>
+      </c>
+      <c r="O78">
+        <v>-0</v>
+      </c>
+      <c r="P78">
+        <v>-223.1927184</v>
+      </c>
+      <c r="Q78">
+        <v>-217.2927184</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.3586212986915089</v>
+      </c>
+      <c r="T78">
+        <v>4.602528740839404</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0</v>
+      </c>
+      <c r="W78">
+        <v>0.2388</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.3507927700192965</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2695571116859621</v>
+      </c>
+      <c r="C79">
+        <v>-746.1226369474356</v>
+      </c>
+      <c r="D79">
+        <v>604.3883630525645</v>
+      </c>
+      <c r="E79">
+        <v>1352.111</v>
+      </c>
+      <c r="F79">
+        <v>1458.611</v>
+      </c>
+      <c r="G79">
+        <v>108.1</v>
+      </c>
+      <c r="H79">
+        <v>1787.8</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>126.5</v>
+      </c>
+      <c r="K79">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L79">
+        <v>120.6</v>
+      </c>
+      <c r="M79">
+        <v>348.3163068000001</v>
+      </c>
+      <c r="N79">
+        <v>-227.7163068000001</v>
+      </c>
+      <c r="O79">
+        <v>-0</v>
+      </c>
+      <c r="P79">
+        <v>-227.7163068000001</v>
+      </c>
+      <c r="Q79">
+        <v>-221.8163068000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3725265725476614</v>
+      </c>
+      <c r="T79">
+        <v>4.802638686093291</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0</v>
+      </c>
+      <c r="W79">
+        <v>0.2388</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.3462370197593057</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2715571116859621</v>
+      </c>
+      <c r="C80">
+        <v>-770.2589335876518</v>
+      </c>
+      <c r="D80">
+        <v>599.1950664123483</v>
+      </c>
+      <c r="E80">
+        <v>1371.054</v>
+      </c>
+      <c r="F80">
+        <v>1477.554</v>
+      </c>
+      <c r="G80">
+        <v>108.1</v>
+      </c>
+      <c r="H80">
+        <v>1787.8</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>126.5</v>
+      </c>
+      <c r="K80">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L80">
+        <v>120.6</v>
+      </c>
+      <c r="M80">
+        <v>352.8398952000001</v>
+      </c>
+      <c r="N80">
+        <v>-232.2398952000001</v>
+      </c>
+      <c r="O80">
+        <v>-0</v>
+      </c>
+      <c r="P80">
+        <v>-232.2398952000001</v>
+      </c>
+      <c r="Q80">
+        <v>-226.3398952000001</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3876959622089188</v>
+      </c>
+      <c r="T80">
+        <v>5.020940444552077</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0</v>
+      </c>
+      <c r="W80">
+        <v>0.2388</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.3417980836085454</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2735571116859621</v>
+      </c>
+      <c r="C81">
+        <v>-794.3067422310116</v>
+      </c>
+      <c r="D81">
+        <v>594.0902577689884</v>
+      </c>
+      <c r="E81">
+        <v>1389.997</v>
+      </c>
+      <c r="F81">
+        <v>1496.497</v>
+      </c>
+      <c r="G81">
+        <v>108.1</v>
+      </c>
+      <c r="H81">
+        <v>1787.8</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>126.5</v>
+      </c>
+      <c r="K81">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L81">
+        <v>120.6</v>
+      </c>
+      <c r="M81">
+        <v>357.3634836000001</v>
+      </c>
+      <c r="N81">
+        <v>-236.7634836000001</v>
+      </c>
+      <c r="O81">
+        <v>-0</v>
+      </c>
+      <c r="P81">
+        <v>-236.7634836000001</v>
+      </c>
+      <c r="Q81">
+        <v>-230.8634836000001</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.4043100556474388</v>
+      </c>
+      <c r="T81">
+        <v>5.260032846673606</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0</v>
+      </c>
+      <c r="W81">
+        <v>0.2388</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.3374715255881841</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2755571116859621</v>
+      </c>
+      <c r="C82">
+        <v>-818.2683053781834</v>
+      </c>
+      <c r="D82">
+        <v>589.0716946218166</v>
+      </c>
+      <c r="E82">
+        <v>1408.94</v>
+      </c>
+      <c r="F82">
+        <v>1515.44</v>
+      </c>
+      <c r="G82">
+        <v>108.1</v>
+      </c>
+      <c r="H82">
+        <v>1787.8</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>126.5</v>
+      </c>
+      <c r="K82">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L82">
+        <v>120.6</v>
+      </c>
+      <c r="M82">
+        <v>361.887072</v>
+      </c>
+      <c r="N82">
+        <v>-241.2870720000001</v>
+      </c>
+      <c r="O82">
+        <v>-0</v>
+      </c>
+      <c r="P82">
+        <v>-241.2870720000001</v>
+      </c>
+      <c r="Q82">
+        <v>-235.387072</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.4225855584298107</v>
+      </c>
+      <c r="T82">
+        <v>5.523034489007285</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0</v>
+      </c>
+      <c r="W82">
+        <v>0.2388</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.3332531315183317</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2775571116859621</v>
+      </c>
+      <c r="C83">
+        <v>-842.1457903906895</v>
+      </c>
+      <c r="D83">
+        <v>584.1372096093105</v>
+      </c>
+      <c r="E83">
+        <v>1427.883</v>
+      </c>
+      <c r="F83">
+        <v>1534.383</v>
+      </c>
+      <c r="G83">
+        <v>108.1</v>
+      </c>
+      <c r="H83">
+        <v>1787.8</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>126.5</v>
+      </c>
+      <c r="K83">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L83">
+        <v>120.6</v>
+      </c>
+      <c r="M83">
+        <v>366.4106604</v>
+      </c>
+      <c r="N83">
+        <v>-245.8106604</v>
+      </c>
+      <c r="O83">
+        <v>-0</v>
+      </c>
+      <c r="P83">
+        <v>-245.8106604</v>
+      </c>
+      <c r="Q83">
+        <v>-239.9106604</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.4427847983471692</v>
+      </c>
+      <c r="T83">
+        <v>5.813720514744512</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0</v>
+      </c>
+      <c r="W83">
+        <v>0.2388</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.3291388953267473</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2795571116859621</v>
+      </c>
+      <c r="C84">
+        <v>-865.9412926118595</v>
+      </c>
+      <c r="D84">
+        <v>579.2847073881405</v>
+      </c>
+      <c r="E84">
+        <v>1446.826</v>
+      </c>
+      <c r="F84">
+        <v>1553.326</v>
+      </c>
+      <c r="G84">
+        <v>108.1</v>
+      </c>
+      <c r="H84">
+        <v>1787.8</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>126.5</v>
+      </c>
+      <c r="K84">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L84">
+        <v>120.6</v>
+      </c>
+      <c r="M84">
+        <v>370.9342488</v>
+      </c>
+      <c r="N84">
+        <v>-250.3342488</v>
+      </c>
+      <c r="O84">
+        <v>-0</v>
+      </c>
+      <c r="P84">
+        <v>-250.3342488</v>
+      </c>
+      <c r="Q84">
+        <v>-244.4342488</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.4652283982553452</v>
+      </c>
+      <c r="T84">
+        <v>6.136704987785873</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0</v>
+      </c>
+      <c r="W84">
+        <v>0.2388</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.325125006359348</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2815571116859621</v>
+      </c>
+      <c r="C85">
+        <v>-889.6568383335067</v>
+      </c>
+      <c r="D85">
+        <v>574.5121616664933</v>
+      </c>
+      <c r="E85">
+        <v>1465.769</v>
+      </c>
+      <c r="F85">
+        <v>1572.269</v>
+      </c>
+      <c r="G85">
+        <v>108.1</v>
+      </c>
+      <c r="H85">
+        <v>1787.8</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>126.5</v>
+      </c>
+      <c r="K85">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L85">
+        <v>120.6</v>
+      </c>
+      <c r="M85">
+        <v>375.4578372</v>
+      </c>
+      <c r="N85">
+        <v>-254.8578372</v>
+      </c>
+      <c r="O85">
+        <v>-0</v>
+      </c>
+      <c r="P85">
+        <v>-254.8578372</v>
+      </c>
+      <c r="Q85">
+        <v>-248.9578372</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4903124216821304</v>
+      </c>
+      <c r="T85">
+        <v>6.49768763412622</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0</v>
+      </c>
+      <c r="W85">
+        <v>0.2388</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.3212078376080306</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2835571116859621</v>
+      </c>
+      <c r="C86">
+        <v>-913.2943876171543</v>
+      </c>
+      <c r="D86">
+        <v>569.8176123828457</v>
+      </c>
+      <c r="E86">
+        <v>1484.712</v>
+      </c>
+      <c r="F86">
+        <v>1591.212</v>
+      </c>
+      <c r="G86">
+        <v>108.1</v>
+      </c>
+      <c r="H86">
+        <v>1787.8</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>126.5</v>
+      </c>
+      <c r="K86">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L86">
+        <v>120.6</v>
+      </c>
+      <c r="M86">
+        <v>379.9814256</v>
+      </c>
+      <c r="N86">
+        <v>-259.3814256000001</v>
+      </c>
+      <c r="O86">
+        <v>-0</v>
+      </c>
+      <c r="P86">
+        <v>-259.3814256000001</v>
+      </c>
+      <c r="Q86">
+        <v>-253.4814256000001</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.5185319480372632</v>
+      </c>
+      <c r="T86">
+        <v>6.903793111259104</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0</v>
+      </c>
+      <c r="W86">
+        <v>0.2388</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.3173839347793634</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2855571116859621</v>
+      </c>
+      <c r="C87">
+        <v>-936.8558369780627</v>
+      </c>
+      <c r="D87">
+        <v>565.1991630219372</v>
+      </c>
+      <c r="E87">
+        <v>1503.655</v>
+      </c>
+      <c r="F87">
+        <v>1610.155</v>
+      </c>
+      <c r="G87">
+        <v>108.1</v>
+      </c>
+      <c r="H87">
+        <v>1787.8</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>126.5</v>
+      </c>
+      <c r="K87">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L87">
+        <v>120.6</v>
+      </c>
+      <c r="M87">
+        <v>384.505014</v>
+      </c>
+      <c r="N87">
+        <v>-263.9050140000001</v>
+      </c>
+      <c r="O87">
+        <v>-0</v>
+      </c>
+      <c r="P87">
+        <v>-263.9050140000001</v>
+      </c>
+      <c r="Q87">
+        <v>-258.0050140000001</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.5505140779064142</v>
+      </c>
+      <c r="T87">
+        <v>7.364045985343045</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0</v>
+      </c>
+      <c r="W87">
+        <v>0.2388</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.3136500061349003</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2875571116859621</v>
+      </c>
+      <c r="C88">
+        <v>-960.3430219397814</v>
+      </c>
+      <c r="D88">
+        <v>560.6549780602186</v>
+      </c>
+      <c r="E88">
+        <v>1522.598</v>
+      </c>
+      <c r="F88">
+        <v>1629.098</v>
+      </c>
+      <c r="G88">
+        <v>108.1</v>
+      </c>
+      <c r="H88">
+        <v>1787.8</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>126.5</v>
+      </c>
+      <c r="K88">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L88">
+        <v>120.6</v>
+      </c>
+      <c r="M88">
+        <v>389.0286024</v>
+      </c>
+      <c r="N88">
+        <v>-268.4286024</v>
+      </c>
+      <c r="O88">
+        <v>-0</v>
+      </c>
+      <c r="P88">
+        <v>-268.4286024</v>
+      </c>
+      <c r="Q88">
+        <v>-262.5286024000001</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.5870650834711579</v>
+      </c>
+      <c r="T88">
+        <v>7.890049270010406</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0</v>
+      </c>
+      <c r="W88">
+        <v>0.2388</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.3100029130403086</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2895571116859621</v>
+      </c>
+      <c r="C89">
+        <v>-983.7577194664489</v>
+      </c>
+      <c r="D89">
+        <v>556.1832805335511</v>
+      </c>
+      <c r="E89">
+        <v>1541.541</v>
+      </c>
+      <c r="F89">
+        <v>1648.041</v>
+      </c>
+      <c r="G89">
+        <v>108.1</v>
+      </c>
+      <c r="H89">
+        <v>1787.8</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>126.5</v>
+      </c>
+      <c r="K89">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L89">
+        <v>120.6</v>
+      </c>
+      <c r="M89">
+        <v>393.5521908</v>
+      </c>
+      <c r="N89">
+        <v>-272.9521908</v>
+      </c>
+      <c r="O89">
+        <v>-0</v>
+      </c>
+      <c r="P89">
+        <v>-272.9521908</v>
+      </c>
+      <c r="Q89">
+        <v>-267.0521908000001</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.629239320661247</v>
+      </c>
+      <c r="T89">
+        <v>8.496976136934283</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0</v>
+      </c>
+      <c r="W89">
+        <v>0.2388</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.306439661166282</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2915571116859622</v>
+      </c>
+      <c r="C90">
+        <v>-1007.101650279621</v>
+      </c>
+      <c r="D90">
+        <v>551.7823497203789</v>
+      </c>
+      <c r="E90">
+        <v>1560.484</v>
+      </c>
+      <c r="F90">
+        <v>1666.984</v>
+      </c>
+      <c r="G90">
+        <v>108.1</v>
+      </c>
+      <c r="H90">
+        <v>1787.8</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>126.5</v>
+      </c>
+      <c r="K90">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L90">
+        <v>120.6</v>
+      </c>
+      <c r="M90">
+        <v>398.0757792</v>
+      </c>
+      <c r="N90">
+        <v>-277.4757792</v>
+      </c>
+      <c r="O90">
+        <v>-0</v>
+      </c>
+      <c r="P90">
+        <v>-277.4757792</v>
+      </c>
+      <c r="Q90">
+        <v>-271.5757792000001</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.6784425973830177</v>
+      </c>
+      <c r="T90">
+        <v>9.205057481678809</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0</v>
+      </c>
+      <c r="W90">
+        <v>0.2388</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3029573922893924</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2935571116859622</v>
+      </c>
+      <c r="C91">
+        <v>-1030.376481065963</v>
+      </c>
+      <c r="D91">
+        <v>547.4505189340371</v>
+      </c>
+      <c r="E91">
+        <v>1579.427</v>
+      </c>
+      <c r="F91">
+        <v>1685.927</v>
+      </c>
+      <c r="G91">
+        <v>108.1</v>
+      </c>
+      <c r="H91">
+        <v>1787.8</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>126.5</v>
+      </c>
+      <c r="K91">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L91">
+        <v>120.6</v>
+      </c>
+      <c r="M91">
+        <v>402.5993676</v>
+      </c>
+      <c r="N91">
+        <v>-281.9993676</v>
+      </c>
+      <c r="O91">
+        <v>-0</v>
+      </c>
+      <c r="P91">
+        <v>-281.9993676</v>
+      </c>
+      <c r="Q91">
+        <v>-276.0993676000001</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.7365919244178376</v>
+      </c>
+      <c r="T91">
+        <v>10.04188088910415</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0</v>
+      </c>
+      <c r="W91">
+        <v>0.2388</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.2995533766456914</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2955571116859621</v>
+      </c>
+      <c r="C92">
+        <v>-1053.583826581764</v>
+      </c>
+      <c r="D92">
+        <v>543.1861734182362</v>
+      </c>
+      <c r="E92">
+        <v>1598.37</v>
+      </c>
+      <c r="F92">
+        <v>1704.87</v>
+      </c>
+      <c r="G92">
+        <v>108.1</v>
+      </c>
+      <c r="H92">
+        <v>1787.8</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>126.5</v>
+      </c>
+      <c r="K92">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L92">
+        <v>120.6</v>
+      </c>
+      <c r="M92">
+        <v>407.122956</v>
+      </c>
+      <c r="N92">
+        <v>-286.522956</v>
+      </c>
+      <c r="O92">
+        <v>-0</v>
+      </c>
+      <c r="P92">
+        <v>-286.522956</v>
+      </c>
+      <c r="Q92">
+        <v>-280.622956</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.8063711168596213</v>
+      </c>
+      <c r="T92">
+        <v>11.04606897801457</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0</v>
+      </c>
+      <c r="W92">
+        <v>0.2388</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.2962250057940726</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2975571116859622</v>
+      </c>
+      <c r="C93">
+        <v>-1076.725251659854</v>
+      </c>
+      <c r="D93">
+        <v>538.9877483401461</v>
+      </c>
+      <c r="E93">
+        <v>1617.313</v>
+      </c>
+      <c r="F93">
+        <v>1723.813</v>
+      </c>
+      <c r="G93">
+        <v>108.1</v>
+      </c>
+      <c r="H93">
+        <v>1787.8</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>126.5</v>
+      </c>
+      <c r="K93">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L93">
+        <v>120.6</v>
+      </c>
+      <c r="M93">
+        <v>411.6465444</v>
+      </c>
+      <c r="N93">
+        <v>-291.0465444</v>
+      </c>
+      <c r="O93">
+        <v>-0</v>
+      </c>
+      <c r="P93">
+        <v>-291.0465444</v>
+      </c>
+      <c r="Q93">
+        <v>-285.1465444</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.8916567965106905</v>
+      </c>
+      <c r="T93">
+        <v>12.27340997557175</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0</v>
+      </c>
+      <c r="W93">
+        <v>0.2388</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.2929697859501819</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2995571116859622</v>
+      </c>
+      <c r="C94">
+        <v>-1099.80227312416</v>
+      </c>
+      <c r="D94">
+        <v>534.8537268758398</v>
+      </c>
+      <c r="E94">
+        <v>1636.256</v>
+      </c>
+      <c r="F94">
+        <v>1742.756</v>
+      </c>
+      <c r="G94">
+        <v>108.1</v>
+      </c>
+      <c r="H94">
+        <v>1787.8</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>126.5</v>
+      </c>
+      <c r="K94">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L94">
+        <v>120.6</v>
+      </c>
+      <c r="M94">
+        <v>416.1701328</v>
+      </c>
+      <c r="N94">
+        <v>-295.5701328</v>
+      </c>
+      <c r="O94">
+        <v>-0</v>
+      </c>
+      <c r="P94">
+        <v>-295.5701328</v>
+      </c>
+      <c r="Q94">
+        <v>-289.6701328</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.9982638960745271</v>
+      </c>
+      <c r="T94">
+        <v>13.80758622251822</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0</v>
+      </c>
+      <c r="W94">
+        <v>0.2388</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.2897853317550712</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.3015571116859621</v>
+      </c>
+      <c r="C95">
+        <v>-1122.816361616829</v>
+      </c>
+      <c r="D95">
+        <v>530.7826383831708</v>
+      </c>
+      <c r="E95">
+        <v>1655.199</v>
+      </c>
+      <c r="F95">
+        <v>1761.699</v>
+      </c>
+      <c r="G95">
+        <v>108.1</v>
+      </c>
+      <c r="H95">
+        <v>1787.8</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>126.5</v>
+      </c>
+      <c r="K95">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L95">
+        <v>120.6</v>
+      </c>
+      <c r="M95">
+        <v>420.6937212</v>
+      </c>
+      <c r="N95">
+        <v>-300.0937212</v>
+      </c>
+      <c r="O95">
+        <v>-0</v>
+      </c>
+      <c r="P95">
+        <v>-300.0937212</v>
+      </c>
+      <c r="Q95">
+        <v>-294.1937212</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>1.135330166942317</v>
+      </c>
+      <c r="T95">
+        <v>15.78009854002082</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0</v>
+      </c>
+      <c r="W95">
+        <v>0.2388</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.2866693604458769</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.3035571116859622</v>
+      </c>
+      <c r="C96">
+        <v>-1145.768943342534</v>
+      </c>
+      <c r="D96">
+        <v>526.7730566574662</v>
+      </c>
+      <c r="E96">
+        <v>1674.142</v>
+      </c>
+      <c r="F96">
+        <v>1780.642</v>
+      </c>
+      <c r="G96">
+        <v>108.1</v>
+      </c>
+      <c r="H96">
+        <v>1787.8</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>126.5</v>
+      </c>
+      <c r="K96">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L96">
+        <v>120.6</v>
+      </c>
+      <c r="M96">
+        <v>425.2173096</v>
+      </c>
+      <c r="N96">
+        <v>-304.6173096</v>
+      </c>
+      <c r="O96">
+        <v>-0</v>
+      </c>
+      <c r="P96">
+        <v>-304.6173096</v>
+      </c>
+      <c r="Q96">
+        <v>-298.7173096</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.318085194766037</v>
+      </c>
+      <c r="T96">
+        <v>18.41011496335763</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0</v>
+      </c>
+      <c r="W96">
+        <v>0.2388</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.2836196863985803</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.3055571116859622</v>
+      </c>
+      <c r="C97">
+        <v>-1168.661401734313</v>
+      </c>
+      <c r="D97">
+        <v>522.8235982656869</v>
+      </c>
+      <c r="E97">
+        <v>1693.085</v>
+      </c>
+      <c r="F97">
+        <v>1799.585</v>
+      </c>
+      <c r="G97">
+        <v>108.1</v>
+      </c>
+      <c r="H97">
+        <v>1787.8</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>126.5</v>
+      </c>
+      <c r="K97">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L97">
+        <v>120.6</v>
+      </c>
+      <c r="M97">
+        <v>429.740898</v>
+      </c>
+      <c r="N97">
+        <v>-309.140898</v>
+      </c>
+      <c r="O97">
+        <v>-0</v>
+      </c>
+      <c r="P97">
+        <v>-309.140898</v>
+      </c>
+      <c r="Q97">
+        <v>-303.240898</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.573942233719245</v>
+      </c>
+      <c r="T97">
+        <v>22.09213795602917</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0</v>
+      </c>
+      <c r="W97">
+        <v>0.2388</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.2806342160154374</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.3075571116859621</v>
+      </c>
+      <c r="C98">
+        <v>-1191.495079045033</v>
+      </c>
+      <c r="D98">
+        <v>518.9329209549662</v>
+      </c>
+      <c r="E98">
+        <v>1712.028</v>
+      </c>
+      <c r="F98">
+        <v>1818.528</v>
+      </c>
+      <c r="G98">
+        <v>108.1</v>
+      </c>
+      <c r="H98">
+        <v>1787.8</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>126.5</v>
+      </c>
+      <c r="K98">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L98">
+        <v>120.6</v>
+      </c>
+      <c r="M98">
+        <v>434.2644864</v>
+      </c>
+      <c r="N98">
+        <v>-313.6644864</v>
+      </c>
+      <c r="O98">
+        <v>-0</v>
+      </c>
+      <c r="P98">
+        <v>-313.6644864</v>
+      </c>
+      <c r="Q98">
+        <v>-307.7644864</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.957727792149051</v>
+      </c>
+      <c r="T98">
+        <v>27.6151724450364</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0</v>
+      </c>
+      <c r="W98">
+        <v>0.2388</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.2777109429319431</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.3095571116859621</v>
+      </c>
+      <c r="C99">
+        <v>-1214.271277868316</v>
+      </c>
+      <c r="D99">
+        <v>515.0997221316841</v>
+      </c>
+      <c r="E99">
+        <v>1730.971</v>
+      </c>
+      <c r="F99">
+        <v>1837.471</v>
+      </c>
+      <c r="G99">
+        <v>108.1</v>
+      </c>
+      <c r="H99">
+        <v>1787.8</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>126.5</v>
+      </c>
+      <c r="K99">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L99">
+        <v>120.6</v>
+      </c>
+      <c r="M99">
+        <v>438.7880748</v>
+      </c>
+      <c r="N99">
+        <v>-318.1880748</v>
+      </c>
+      <c r="O99">
+        <v>-0</v>
+      </c>
+      <c r="P99">
+        <v>-318.1880748</v>
+      </c>
+      <c r="Q99">
+        <v>-312.2880748</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.597370389532069</v>
+      </c>
+      <c r="T99">
+        <v>36.8202299267152</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0</v>
+      </c>
+      <c r="W99">
+        <v>0.2388</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.2748479435202736</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.3115571116859621</v>
+      </c>
+      <c r="C100">
+        <v>-1236.991262592547</v>
+      </c>
+      <c r="D100">
+        <v>511.3227374074527</v>
+      </c>
+      <c r="E100">
+        <v>1749.914</v>
+      </c>
+      <c r="F100">
+        <v>1856.414</v>
+      </c>
+      <c r="G100">
+        <v>108.1</v>
+      </c>
+      <c r="H100">
+        <v>1787.8</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>126.5</v>
+      </c>
+      <c r="K100">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L100">
+        <v>120.6</v>
+      </c>
+      <c r="M100">
+        <v>443.3116632</v>
+      </c>
+      <c r="N100">
+        <v>-322.7116632</v>
+      </c>
+      <c r="O100">
+        <v>-0</v>
+      </c>
+      <c r="P100">
+        <v>-322.7116632</v>
+      </c>
+      <c r="Q100">
+        <v>-316.8116632</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.876655584298103</v>
+      </c>
+      <c r="T100">
+        <v>55.2303448900728</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0</v>
+      </c>
+      <c r="W100">
+        <v>0.2388</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.272043372668026</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.3135571116859621</v>
+      </c>
+      <c r="C101">
+        <v>-1259.656260791392</v>
+      </c>
+      <c r="D101">
+        <v>507.600739208608</v>
+      </c>
+      <c r="E101">
+        <v>1768.857</v>
+      </c>
+      <c r="F101">
+        <v>1875.357</v>
+      </c>
+      <c r="G101">
+        <v>108.1</v>
+      </c>
+      <c r="H101">
+        <v>1787.8</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>126.5</v>
+      </c>
+      <c r="K101">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="L101">
+        <v>120.6</v>
+      </c>
+      <c r="M101">
+        <v>447.8352516</v>
+      </c>
+      <c r="N101">
+        <v>-327.2352516</v>
+      </c>
+      <c r="O101">
+        <v>-0</v>
+      </c>
+      <c r="P101">
+        <v>-327.2352516</v>
+      </c>
+      <c r="Q101">
+        <v>-321.3352516</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>7.714511168596206</v>
+      </c>
+      <c r="T101">
+        <v>110.4606897801456</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0</v>
+      </c>
+      <c r="W101">
+        <v>0.2388</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.2692954598127935</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
